--- a/Data/biomass_filtered.xlsx
+++ b/Data/biomass_filtered.xlsx
@@ -467,10 +467,8 @@
           <t>0.376</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>20.751313846153849</t>
-        </is>
+      <c r="J2">
+        <v>20.75131384615385</v>
       </c>
       <c r="K2">
         <v>14.34931276595745</v>
@@ -525,10 +523,8 @@
           <t>0.29199999999999998</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>18.657767538461535</t>
-        </is>
+      <c r="J3">
+        <v>18.65776753846153</v>
       </c>
       <c r="K3">
         <v>16.6130806849315</v>
@@ -583,10 +579,8 @@
           <t>0.33100000000000002</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>25.76600353846154</t>
-        </is>
+      <c r="J4">
+        <v>25.76600353846154</v>
       </c>
       <c r="K4">
         <v>20.23915685800604</v>
@@ -641,10 +635,8 @@
           <t>0.32200000000000001</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>19.67347430769231</t>
-        </is>
+      <c r="J5">
+        <v>19.67347430769231</v>
       </c>
       <c r="K5">
         <v>15.88541403726708</v>
@@ -699,10 +691,8 @@
           <t>0.29699999999999999</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>18.560884153846157</t>
-        </is>
+      <c r="J6">
+        <v>18.56088415384616</v>
       </c>
       <c r="K6">
         <v>16.24858545454546</v>
@@ -757,10 +747,8 @@
           <t>0.44</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>22.163301230769232</t>
-        </is>
+      <c r="J7">
+        <v>22.16330123076923</v>
       </c>
       <c r="K7">
         <v>13.09649618181818</v>
@@ -815,10 +803,8 @@
           <t>0.4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>18.389365384615385</t>
-        </is>
+      <c r="J8">
+        <v>18.38936538461538</v>
       </c>
       <c r="K8">
         <v>11.9530875</v>
@@ -873,10 +859,8 @@
           <t>0.28199999999999997</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>15.833650153846154</t>
-        </is>
+      <c r="J9">
+        <v>15.83365015384615</v>
       </c>
       <c r="K9">
         <v>14.59840085106383</v>
@@ -931,10 +915,8 @@
           <t>0.46500000000000002</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15.205999846153848</t>
-        </is>
+      <c r="J10">
+        <v>15.20599984615385</v>
       </c>
       <c r="K10">
         <v>8.502279483870968</v>
@@ -989,10 +971,8 @@
           <t>0.33900000000000002</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.171115999999998</t>
-        </is>
+      <c r="J11">
+        <v>13.171116</v>
       </c>
       <c r="K11">
         <v>10.10174088495575</v>
@@ -1047,10 +1027,8 @@
           <t>0.33800000000000002</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22.653089999999999</t>
-        </is>
+      <c r="J12">
+        <v>22.65309</v>
       </c>
       <c r="K12">
         <v>17.42545384615384</v>
@@ -1105,10 +1083,8 @@
           <t>0.34899999999999998</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>25.593343846153846</t>
-        </is>
+      <c r="J13">
+        <v>25.59334384615385</v>
       </c>
       <c r="K13">
         <v>19.06667449856734</v>
@@ -1163,10 +1139,8 @@
           <t>0.40300000000000002</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>18.820254000000002</t>
-        </is>
+      <c r="J14">
+        <v>18.820254</v>
       </c>
       <c r="K14">
         <v>12.14209935483871</v>
@@ -1221,10 +1195,8 @@
           <t>0.432</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>21.047383384615383</t>
-        </is>
+      <c r="J15">
+        <v>21.04738338461538</v>
       </c>
       <c r="K15">
         <v>12.66740666666667</v>
@@ -1279,10 +1251,8 @@
           <t>0.40100000000000002</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>17.229236769230766</t>
-        </is>
+      <c r="J16">
+        <v>17.22923676923077</v>
       </c>
       <c r="K16">
         <v>11.17107620947631</v>
@@ -1337,10 +1307,8 @@
           <t>0.33900000000000002</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>16.727610923076924</t>
-        </is>
+      <c r="J17">
+        <v>16.72761092307692</v>
       </c>
       <c r="K17">
         <v>12.82943610619469</v>
@@ -1395,10 +1363,8 @@
           <t>0.38900000000000001</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>15.925922307692309</t>
-        </is>
+      <c r="J18">
+        <v>15.92592230769231</v>
       </c>
       <c r="K18">
         <v>10.64457532133676</v>
@@ -1453,10 +1419,8 @@
           <t>0.29599999999999999</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>13.914807692307694</t>
-        </is>
+      <c r="J19">
+        <v>13.91480769230769</v>
       </c>
       <c r="K19">
         <v>12.22246621621622</v>
@@ -1511,10 +1475,8 @@
           <t>0.44500000000000001</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>11.300810307692307</t>
-        </is>
+      <c r="J20">
+        <v>11.30081030769231</v>
       </c>
       <c r="K20">
         <v>6.602720629213483</v>
@@ -1569,10 +1531,8 @@
           <t>0.39400000000000002</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>16.781424461538464</t>
-        </is>
+      <c r="J21">
+        <v>16.78142446153846</v>
       </c>
       <c r="K21">
         <v>11.07403644670051</v>
@@ -1627,10 +1587,8 @@
           <t>0.38700000000000001</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>11.665240153846154</t>
-        </is>
+      <c r="J22">
+        <v>11.66524015384615</v>
       </c>
       <c r="K22">
         <v>7.837112248062017</v>
@@ -1685,10 +1643,8 @@
           <t>0.52100000000000002</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>10.701968307692306</t>
-        </is>
+      <c r="J23">
+        <v>10.70196830769231</v>
       </c>
       <c r="K23">
         <v>5.340713550863723</v>
@@ -1743,10 +1699,8 @@
           <t>0.42499999999999999</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>13.53297876923077</t>
-        </is>
+      <c r="J24">
+        <v>13.53297876923077</v>
       </c>
       <c r="K24">
         <v>8.278998776470589</v>
@@ -1801,10 +1755,8 @@
           <t>0.28299999999999997</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>15.014705076923075</t>
-        </is>
+      <c r="J25">
+        <v>15.01470507692308</v>
       </c>
       <c r="K25">
         <v>13.79442869257951</v>
@@ -1859,10 +1811,8 @@
           <t>0.48899999999999999</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>17.079443076923077</t>
-        </is>
+      <c r="J26">
+        <v>17.07944307692308</v>
       </c>
       <c r="K26">
         <v>9.081094478527607</v>
@@ -1917,10 +1867,8 @@
           <t>0.40400000000000003</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>12.875759538461537</t>
-        </is>
+      <c r="J27">
+        <v>12.87575953846154</v>
       </c>
       <c r="K27">
         <v>8.286379900990099</v>
@@ -1975,10 +1923,8 @@
           <t>0.56000000000000005</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>11.627969999999996</t>
-        </is>
+      <c r="J28">
+        <v>11.62797</v>
       </c>
       <c r="K28">
         <v>5.398700357142856</v>
@@ -2033,10 +1979,8 @@
           <t>0.33300000000000002</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>9.1264010769230772</t>
-        </is>
+      <c r="J29">
+        <v>9.126401076923077</v>
       </c>
       <c r="K29">
         <v>7.125718558558559</v>
@@ -2091,10 +2035,8 @@
           <t>0.48199999999999998</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>6.3378424615384619</t>
-        </is>
+      <c r="J30">
+        <v>6.337842461538462</v>
       </c>
       <c r="K30">
         <v>3.418753195020747</v>
@@ -2149,10 +2091,8 @@
           <t>0.44500000000000001</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>9.9949763076923066</t>
-        </is>
+      <c r="J31">
+        <v>9.994976307692307</v>
       </c>
       <c r="K31">
         <v>5.839761438202246</v>
@@ -2207,10 +2147,8 @@
           <t>0.20100000000000001</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>8.9258363076923075</t>
-        </is>
+      <c r="J32">
+        <v>8.925836307692308</v>
       </c>
       <c r="K32">
         <v>11.54585791044776</v>
@@ -2265,10 +2203,8 @@
           <t>0.25600000000000001</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>12.673673538461536</t>
-        </is>
+      <c r="J33">
+        <v>12.67367353846154</v>
       </c>
       <c r="K33">
         <v>12.8716996875</v>
@@ -2323,10 +2259,8 @@
           <t>0.16400000000000001</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>8.0234136923076935</t>
-        </is>
+      <c r="J34">
+        <v>8.023413692307694</v>
       </c>
       <c r="K34">
         <v>12.72004609756098</v>
@@ -2381,10 +2315,8 @@
           <t>0.21</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>11.831387076923074</t>
-        </is>
+      <c r="J35">
+        <v>11.83138707692307</v>
       </c>
       <c r="K35">
         <v>14.648384</v>
@@ -2439,10 +2371,8 @@
           <t>0.22800000000000001</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>11.876643692307693</t>
-        </is>
+      <c r="J36">
+        <v>11.87664369230769</v>
       </c>
       <c r="K36">
         <v>13.54354105263158</v>
@@ -2497,10 +2427,8 @@
           <t>0.188</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.1942572307692316</t>
-        </is>
+      <c r="J37">
+        <v>5.194257230769232</v>
       </c>
       <c r="K37">
         <v>7.183547234042554</v>
@@ -2555,10 +2483,8 @@
           <t>0.33</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>6.386426769230769</t>
-        </is>
+      <c r="J38">
+        <v>6.386426769230769</v>
       </c>
       <c r="K38">
         <v>5.031730181818181</v>
@@ -2613,10 +2539,8 @@
           <t>0.35</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>6.1504933846153849</t>
-        </is>
+      <c r="J39">
+        <v>6.150493384615385</v>
       </c>
       <c r="K39">
         <v>4.568937942857143</v>
@@ -2671,10 +2595,8 @@
           <t>0.308</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>10.983253384615384</t>
-        </is>
+      <c r="J40">
+        <v>10.98325338461538</v>
       </c>
       <c r="K40">
         <v>9.271577532467532</v>
@@ -2729,10 +2651,8 @@
           <t>0.23699999999999999</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>6.8215463076923095</t>
-        </is>
+      <c r="J41">
+        <v>6.82154630769231</v>
       </c>
       <c r="K41">
         <v>7.483552911392407</v>
@@ -2787,10 +2707,8 @@
           <t>0.29799999999999999</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>5.7060563076923074</t>
-        </is>
+      <c r="J42">
+        <v>5.706056307692307</v>
       </c>
       <c r="K42">
         <v>4.978438389261745</v>
@@ -2845,10 +2763,8 @@
           <t>0.22700000000000001</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>5.1885526153846158</t>
-        </is>
+      <c r="J43">
+        <v>5.188552615384616</v>
       </c>
       <c r="K43">
         <v>5.942835594713657</v>
@@ -2903,10 +2819,8 @@
           <t>0.26400000000000001</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>13.369684153846155</t>
-        </is>
+      <c r="J44">
+        <v>13.36968415384615</v>
       </c>
       <c r="K44">
         <v>13.16711318181818</v>
@@ -2961,10 +2875,8 @@
           <t>0.24399999999999999</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>11.450461384615386</t>
-        </is>
+      <c r="J45">
+        <v>11.45046138461539</v>
       </c>
       <c r="K45">
         <v>12.20131131147541</v>
@@ -3019,10 +2931,8 @@
           <t>0.312</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>9.4432924615384621</t>
-        </is>
+      <c r="J46">
+        <v>9.443292461538462</v>
       </c>
       <c r="K46">
         <v>7.869410384615385</v>
@@ -3077,10 +2987,8 @@
           <t>0.29499999999999998</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>15.137021538461537</t>
-        </is>
+      <c r="J47">
+        <v>15.13702153846154</v>
       </c>
       <c r="K47">
         <v>13.34110372881356</v>
@@ -3135,10 +3043,8 @@
           <t>0.26700000000000002</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>7.3722793846153847</t>
-        </is>
+      <c r="J48">
+        <v>7.372279384615385</v>
       </c>
       <c r="K48">
         <v>7.178998651685394</v>
@@ -3193,10 +3099,8 @@
           <t>0.35699999999999998</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>9.7591380000000001</t>
-        </is>
+      <c r="J49">
+        <v>9.759138</v>
       </c>
       <c r="K49">
         <v>7.107495462184874</v>
@@ -3251,10 +3155,8 @@
           <t>0.24</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>15.317525076923079</t>
-        </is>
+      <c r="J50">
+        <v>15.31752507692308</v>
       </c>
       <c r="K50">
         <v>16.5939855</v>
@@ -3309,10 +3211,8 @@
           <t>0.34100000000000003</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>6.7317461538461556</t>
-        </is>
+      <c r="J51">
+        <v>6.731746153846156</v>
       </c>
       <c r="K51">
         <v>5.132709677419355</v>
@@ -3367,10 +3267,8 @@
           <t>0.38900000000000001</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>6.4834527692307695</t>
-        </is>
+      <c r="J52">
+        <v>6.48345276923077</v>
       </c>
       <c r="K52">
         <v>4.333413161953728</v>
@@ -3425,10 +3323,8 @@
           <t>0.33700000000000002</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>7.8838883076923052</t>
-        </is>
+      <c r="J53">
+        <v>7.883888307692305</v>
       </c>
       <c r="K53">
         <v>6.082525103857565</v>
@@ -3483,10 +3379,8 @@
           <t>0.32800000000000001</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>4.3636652307692314</t>
-        </is>
+      <c r="J54">
+        <v>4.363665230769231</v>
       </c>
       <c r="K54">
         <v>3.459002926829269</v>
@@ -3541,10 +3435,8 @@
           <t>0.39500000000000002</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>7.8225636923076918</t>
-        </is>
+      <c r="J55">
+        <v>7.822563692307692</v>
       </c>
       <c r="K55">
         <v>5.149029265822784</v>
@@ -3599,10 +3491,8 @@
           <t>0.38100000000000001</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>8.9733747692307677</t>
-        </is>
+      <c r="J56">
+        <v>8.973374769230768</v>
       </c>
       <c r="K56">
         <v>6.123562834645669</v>
@@ -3657,10 +3547,8 @@
           <t>0.38700000000000001</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>7.7004373846153831</t>
-        </is>
+      <c r="J57">
+        <v>7.700437384615383</v>
       </c>
       <c r="K57">
         <v>5.173420465116278</v>
@@ -3715,10 +3603,8 @@
           <t>0.501</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>4.8482247692307698</t>
-        </is>
+      <c r="J58">
+        <v>4.84822476923077</v>
       </c>
       <c r="K58">
         <v>2.516044790419162</v>
@@ -3773,10 +3659,8 @@
           <t>0.35299999999999998</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>6.4303047692307693</t>
-        </is>
+      <c r="J59">
+        <v>6.430304769230769</v>
       </c>
       <c r="K59">
         <v>4.736201813031162</v>
@@ -3831,10 +3715,8 @@
           <t>0.374</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>10.509817846153846</t>
-        </is>
+      <c r="J60">
+        <v>10.50981784615385</v>
       </c>
       <c r="K60">
         <v>7.306290481283422</v>
@@ -3889,10 +3771,8 @@
           <t>0.30399999999999999</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>10.261571999999999</t>
-        </is>
+      <c r="J61">
+        <v>10.261572</v>
       </c>
       <c r="K61">
         <v>8.77634447368421</v>
@@ -3947,10 +3827,8 @@
           <t>0.49299999999999999</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>8.168833846153845</t>
-        </is>
+      <c r="J62">
+        <v>8.168833846153845</v>
       </c>
       <c r="K62">
         <v>4.308107099391481</v>
@@ -4005,10 +3883,8 @@
           <t>0.54700000000000004</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>11.577484153846154</t>
-        </is>
+      <c r="J63">
+        <v>11.57748415384615</v>
       </c>
       <c r="K63">
         <v>5.503008921389396</v>
@@ -4063,10 +3939,8 @@
           <t>0.54500000000000004</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>8.7874518461538464</t>
-        </is>
+      <c r="J64">
+        <v>8.787451846153846</v>
       </c>
       <c r="K64">
         <v>4.192178862385321</v>
@@ -4121,10 +3995,8 @@
           <t>0.59899999999999998</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>7.1325429230769233</t>
-        </is>
+      <c r="J65">
+        <v>7.132542923076923</v>
       </c>
       <c r="K65">
         <v>3.095928480801336</v>
@@ -4179,10 +4051,8 @@
           <t>0.499</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>5.9979424615384618</t>
-        </is>
+      <c r="J66">
+        <v>5.997942461538462</v>
       </c>
       <c r="K66">
         <v>3.125180440881764</v>
@@ -4237,10 +4107,8 @@
           <t>0.62</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>16.853255076923077</t>
-        </is>
+      <c r="J67">
+        <v>16.85325507692308</v>
       </c>
       <c r="K67">
         <v>7.067494064516129</v>
@@ -4295,10 +4163,8 @@
           <t>0.57199999999999995</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>5.1325523076923076</t>
-        </is>
+      <c r="J68">
+        <v>5.132552307692308</v>
       </c>
       <c r="K68">
         <v>2.332978321678322</v>
@@ -4353,10 +4219,8 @@
           <t>0.63300000000000001</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>12.535574307692309</t>
-        </is>
+      <c r="J69">
+        <v>12.53557430769231</v>
       </c>
       <c r="K69">
         <v>5.148893080568721</v>
@@ -4411,10 +4275,8 @@
           <t>0.54800000000000004</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>11.580859384615383</t>
-        </is>
+      <c r="J70">
+        <v>11.58085938461538</v>
       </c>
       <c r="K70">
         <v>5.494568321167883</v>
@@ -4469,10 +4331,8 @@
           <t>0.47899999999999998</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>8.6481166153846143</t>
-        </is>
+      <c r="J71">
+        <v>8.648116615384614</v>
       </c>
       <c r="K71">
         <v>4.694176033402923</v>
@@ -4527,10 +4387,8 @@
           <t>0.44700000000000001</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>12.348082615384614</t>
-        </is>
+      <c r="J72">
+        <v>12.34808261538461</v>
       </c>
       <c r="K72">
         <v>7.182329932885906</v>
@@ -4585,10 +4443,8 @@
           <t>0.52800000000000002</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>13.95378923076923</t>
-        </is>
+      <c r="J73">
+        <v>13.95378923076923</v>
       </c>
       <c r="K73">
         <v>6.87118409090909</v>
@@ -4643,10 +4499,8 @@
           <t>0.50900000000000001</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>11.662910769230772</t>
-        </is>
+      <c r="J74">
+        <v>11.66291076923077</v>
       </c>
       <c r="K74">
         <v>5.957478978388999</v>
@@ -4701,10 +4555,8 @@
           <t>0.51600000000000001</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>7.5927627692307675</t>
-        </is>
+      <c r="J75">
+        <v>7.592762769230768</v>
       </c>
       <c r="K75">
         <v>3.825810697674418</v>
@@ -4759,10 +4611,8 @@
           <t>0.36899999999999999</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>9.2157733846153853</t>
-        </is>
+      <c r="J76">
+        <v>9.215773384615385</v>
       </c>
       <c r="K76">
         <v>6.493498861788619</v>
@@ -4817,10 +4667,8 @@
           <t>0.35699999999999998</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>9.0646486153846162</t>
-        </is>
+      <c r="J77">
+        <v>9.064648615384616</v>
       </c>
       <c r="K77">
         <v>6.60170487394958</v>
@@ -4875,10 +4723,8 @@
           <t>0.52100000000000002</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>14.871138923076925</t>
-        </is>
+      <c r="J78">
+        <v>14.87113892307693</v>
       </c>
       <c r="K78">
         <v>7.421297735124761</v>
@@ -4933,10 +4779,8 @@
           <t>0.33700000000000002</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>12.981009692307692</t>
-        </is>
+      <c r="J79">
+        <v>12.98100969230769</v>
       </c>
       <c r="K79">
         <v>10.01502231454006</v>
@@ -4991,10 +4835,8 @@
           <t>0.501</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>18.077227846153846</t>
-        </is>
+      <c r="J80">
+        <v>18.07722784615385</v>
       </c>
       <c r="K80">
         <v>9.381395688622755</v>
@@ -5049,10 +4891,8 @@
           <t>0.51100000000000001</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>17.226051692307692</t>
-        </is>
+      <c r="J81">
+        <v>17.22605169230769</v>
       </c>
       <c r="K81">
         <v>8.764722974559687</v>
@@ -5107,10 +4947,8 @@
           <t>0.28399999999999997</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>18.635852307692307</t>
-        </is>
+      <c r="J82">
+        <v>18.63585230769231</v>
       </c>
       <c r="K82">
         <v>17.06099154929578</v>
@@ -5165,10 +5003,8 @@
           <t>0.318</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>16.109325692307692</t>
-        </is>
+      <c r="J83">
+        <v>16.10932569230769</v>
       </c>
       <c r="K83">
         <v>13.17114679245283</v>
@@ -5223,10 +5059,8 @@
           <t>0.42899999999999999</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>18.462859846153844</t>
-        </is>
+      <c r="J84">
+        <v>18.46285984615384</v>
       </c>
       <c r="K84">
         <v>11.18961202797203</v>
@@ -5281,10 +5115,8 @@
           <t>0.42199999999999999</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>16.806477230769229</t>
-        </is>
+      <c r="J85">
+        <v>16.80647723076923</v>
       </c>
       <c r="K85">
         <v>10.35470161137441</v>
@@ -5339,10 +5171,8 @@
           <t>0.41899999999999998</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>8.0235087692307694</t>
-        </is>
+      <c r="J86">
+        <v>8.023508769230769</v>
       </c>
       <c r="K86">
         <v>4.978788257756563</v>
@@ -5397,10 +5227,8 @@
           <t>0.40500000000000003</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>15.047316461538463</t>
-        </is>
+      <c r="J87">
+        <v>15.04731646153846</v>
       </c>
       <c r="K87">
         <v>9.66000562962963</v>
@@ -5455,10 +5283,8 @@
           <t>0.315</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>16.554380769230765</t>
-        </is>
+      <c r="J88">
+        <v>16.55438076923076</v>
       </c>
       <c r="K88">
         <v>13.66393333333333</v>
@@ -5513,10 +5339,8 @@
           <t>0.29199999999999998</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>12.294934615384616</t>
-        </is>
+      <c r="J89">
+        <v>12.29493461538462</v>
       </c>
       <c r="K89">
         <v>10.94754452054795</v>
@@ -5571,10 +5395,8 @@
           <t>0.374</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>18.097146461538461</t>
-        </is>
+      <c r="J90">
+        <v>18.09714646153846</v>
       </c>
       <c r="K90">
         <v>12.58090395721925</v>
@@ -5629,10 +5451,8 @@
           <t>0.46899999999999997</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>15.495699230769233</t>
-        </is>
+      <c r="J91">
+        <v>15.49569923076923</v>
       </c>
       <c r="K91">
         <v>8.590366311300642</v>
@@ -5687,10 +5507,8 @@
           <t>0.35</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>7.0542470769230761</t>
-        </is>
+      <c r="J92">
+        <v>7.054247076923076</v>
       </c>
       <c r="K92">
         <v>5.240297828571428</v>
@@ -5745,10 +5563,8 @@
           <t>0.13500000000000001</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>10.413790153846152</t>
-        </is>
+      <c r="J93">
+        <v>10.41379015384615</v>
       </c>
       <c r="K93">
         <v>20.05618844444444</v>
@@ -5803,10 +5619,8 @@
           <t>0.41299999999999998</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>7.6434387692307686</t>
-        </is>
+      <c r="J94">
+        <v>7.643438769230769</v>
       </c>
       <c r="K94">
         <v>4.811850072639225</v>
@@ -5861,10 +5675,8 @@
           <t>0.28799999999999998</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>13.407810000000001</t>
-        </is>
+      <c r="J95">
+        <v>13.40781</v>
       </c>
       <c r="K95">
         <v>12.10427291666667</v>
@@ -5919,10 +5731,8 @@
           <t>0.14099999999999999</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>17.490365538461539</t>
-        </is>
+      <c r="J96">
+        <v>17.49036553846154</v>
       </c>
       <c r="K96">
         <v>32.25173787234043</v>
@@ -5977,10 +5787,8 @@
           <t>0.10299999999999999</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>15.099323538461537</t>
-        </is>
+      <c r="J97">
+        <v>15.09932353846154</v>
       </c>
       <c r="K97">
         <v>38.1147972815534</v>
@@ -6035,10 +5843,8 @@
           <t>0.16300000000000001</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>14.527483384615385</t>
-        </is>
+      <c r="J98">
+        <v>14.52748338461539</v>
       </c>
       <c r="K98">
         <v>23.17267288343558</v>
@@ -6093,10 +5899,8 @@
           <t>0.17499999999999999</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>13.583654769230769</t>
-        </is>
+      <c r="J99">
+        <v>13.58365476923077</v>
       </c>
       <c r="K99">
         <v>20.18142994285714</v>
@@ -6151,10 +5955,8 @@
           <t>0.13800000000000001</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>9.809196</t>
-        </is>
+      <c r="J100">
+        <v>9.809196</v>
       </c>
       <c r="K100">
         <v>18.48109391304348</v>
@@ -6209,10 +6011,8 @@
           <t>0.154</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>14.731803692307693</t>
-        </is>
+      <c r="J101">
+        <v>14.73180369230769</v>
       </c>
       <c r="K101">
         <v>24.87187636363636</v>
@@ -6267,10 +6067,8 @@
           <t>0.317</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>17.028862153846152</t>
-        </is>
+      <c r="J102">
+        <v>17.02886215384615</v>
       </c>
       <c r="K102">
         <v>13.96689009463722</v>
@@ -6325,10 +6123,8 @@
           <t>0.221</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>21.38219676923077</t>
-        </is>
+      <c r="J103">
+        <v>21.38219676923077</v>
       </c>
       <c r="K103">
         <v>25.15552561085973</v>
@@ -6383,10 +6179,8 @@
           <t>0.22700000000000001</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>17.547839538461538</t>
-        </is>
+      <c r="J104">
+        <v>17.54783953846154</v>
       </c>
       <c r="K104">
         <v>20.09884704845815</v>
@@ -6441,10 +6235,8 @@
           <t>0.185</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>13.831472769230768</t>
-        </is>
+      <c r="J105">
+        <v>13.83147276923077</v>
       </c>
       <c r="K105">
         <v>19.43882659459459</v>
@@ -6499,10 +6291,8 @@
           <t>0.22900000000000001</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>16.82501723076923</t>
-        </is>
+      <c r="J106">
+        <v>16.82501723076923</v>
       </c>
       <c r="K106">
         <v>19.10263965065502</v>
@@ -6557,10 +6347,8 @@
           <t>0.192</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>10.962526615384613</t>
-        </is>
+      <c r="J107">
+        <v>10.96252661538461</v>
       </c>
       <c r="K107">
         <v>14.845088125</v>
@@ -6615,10 +6403,8 @@
           <t>0.32200000000000001</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>11.314834153846151</t>
-        </is>
+      <c r="J108">
+        <v>11.31483415384615</v>
       </c>
       <c r="K108">
         <v>9.136201490683229</v>
@@ -6673,10 +6459,8 @@
           <t>0.34300000000000003</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>10.684949538461538</t>
-        </is>
+      <c r="J109">
+        <v>10.68494953846154</v>
       </c>
       <c r="K109">
         <v>8.099378658892128</v>
@@ -6731,10 +6515,8 @@
           <t>0.60499999999999998</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>11.724235384615382</t>
-        </is>
+      <c r="J110">
+        <v>11.72423538461538</v>
       </c>
       <c r="K110">
         <v>5.038514380165288</v>
@@ -6789,10 +6571,8 @@
           <t>0.47499999999999998</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>11.554570615384618</t>
-        </is>
+      <c r="J111">
+        <v>11.55457061538462</v>
       </c>
       <c r="K111">
         <v>6.324607073684212</v>
@@ -6847,10 +6627,8 @@
           <t>0.24</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>13.080697846153845</t>
-        </is>
+      <c r="J112">
+        <v>13.08069784615384</v>
       </c>
       <c r="K112">
         <v>14.170756</v>
@@ -6905,10 +6683,8 @@
           <t>0.42599999999999999</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>16.370739692307691</t>
-        </is>
+      <c r="J113">
+        <v>16.37073969230769</v>
       </c>
       <c r="K113">
         <v>9.991531267605634</v>
@@ -6963,10 +6739,8 @@
           <t>0.23100000000000001</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>16.824399230769231</t>
-        </is>
+      <c r="J114">
+        <v>16.82439923076923</v>
       </c>
       <c r="K114">
         <v>18.93655324675325</v>
@@ -7021,10 +6795,8 @@
           <t>0.41399999999999998</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>14.453133230769231</t>
-        </is>
+      <c r="J115">
+        <v>14.45313323076923</v>
       </c>
       <c r="K115">
         <v>9.07684695652174</v>
@@ -7079,10 +6851,8 @@
           <t>0.28699999999999998</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>13.661142461538457</t>
-        </is>
+      <c r="J116">
+        <v>13.66114246153846</v>
       </c>
       <c r="K116">
         <v>12.37594787456446</v>
@@ -7137,10 +6907,8 @@
           <t>0.60599999999999998</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>13.841693538461538</t>
-        </is>
+      <c r="J117">
+        <v>13.84169353846154</v>
       </c>
       <c r="K117">
         <v>5.938680396039604</v>
@@ -7195,10 +6963,8 @@
           <t>0.54600000000000004</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>16.853825538461539</t>
-        </is>
+      <c r="J118">
+        <v>16.85382553846154</v>
       </c>
       <c r="K118">
         <v>8.025631208791209</v>
@@ -7253,10 +7019,8 @@
           <t>0.34200000000000003</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>13.363836923076923</t>
-        </is>
+      <c r="J119">
+        <v>13.36383692307692</v>
       </c>
       <c r="K119">
         <v>10.15964210526316</v>
@@ -7311,10 +7075,8 @@
           <t>0.44700000000000001</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>11.685491538461536</t>
-        </is>
+      <c r="J120">
+        <v>11.68549153846154</v>
       </c>
       <c r="K120">
         <v>6.796930201342281</v>
@@ -7369,10 +7131,8 @@
           <t>0.22500000000000001</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>11.905261846153847</t>
-        </is>
+      <c r="J121">
+        <v>11.90526184615385</v>
       </c>
       <c r="K121">
         <v>13.75719146666667</v>
@@ -7427,10 +7187,8 @@
           <t>0.61</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>16.62236076923077</t>
-        </is>
+      <c r="J122">
+        <v>16.62236076923077</v>
       </c>
       <c r="K122">
         <v>7.084940655737705</v>
@@ -7485,10 +7243,8 @@
           <t>0.55400000000000005</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>11.268674307692306</t>
-        </is>
+      <c r="J123">
+        <v>11.26867430769231</v>
       </c>
       <c r="K123">
         <v>5.288547509025269</v>
@@ -7543,10 +7299,8 @@
           <t>0.44600000000000001</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>12.859026</t>
-        </is>
+      <c r="J124">
+        <v>12.859026</v>
       </c>
       <c r="K124">
         <v>7.496293183856502</v>
@@ -7601,10 +7355,8 @@
           <t>0.64</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>14.458457538461538</t>
-        </is>
+      <c r="J125">
+        <v>14.45845753846154</v>
       </c>
       <c r="K125">
         <v>5.873748375</v>
@@ -7659,10 +7411,8 @@
           <t>0.66400000000000003</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>14.283183230769229</t>
-        </is>
+      <c r="J126">
+        <v>14.28318323076923</v>
       </c>
       <c r="K126">
         <v>5.592812710843372</v>
@@ -7717,10 +7467,8 @@
           <t>0.59399999999999997</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>8.8741144615384613</t>
-        </is>
+      <c r="J127">
+        <v>8.874114461538461</v>
       </c>
       <c r="K127">
         <v>3.884292525252525</v>
@@ -7775,10 +7523,8 @@
           <t>0.69299999999999995</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>14.452943076923077</t>
-        </is>
+      <c r="J128">
+        <v>14.45294307692308</v>
       </c>
       <c r="K128">
         <v>5.422460606060607</v>
@@ -7833,10 +7579,8 @@
           <t>0.67200000000000004</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>25.470551999999998</t>
-        </is>
+      <c r="J129">
+        <v>25.470552</v>
       </c>
       <c r="K129">
         <v>9.854677857142855</v>
@@ -7891,10 +7635,8 @@
           <t>0.70599999999999996</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>12.058097999999998</t>
-        </is>
+      <c r="J130">
+        <v>12.058098</v>
       </c>
       <c r="K130">
         <v>4.440659320113314</v>
@@ -7949,10 +7691,8 @@
           <t>0.52400000000000002</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>16.84170323076923</t>
-        </is>
+      <c r="J131">
+        <v>16.84170323076923</v>
       </c>
       <c r="K131">
         <v>8.35657030534351</v>
@@ -8007,10 +7747,8 @@
           <t>0.92900000000000005</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>15.771897692307691</t>
-        </is>
+      <c r="J132">
+        <v>15.77189769230769</v>
       </c>
       <c r="K132">
         <v>4.414094079655543</v>
@@ -8065,10 +7803,8 @@
           <t>0.73899999999999999</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>17.447058000000002</t>
-        </is>
+      <c r="J133">
+        <v>17.447058</v>
       </c>
       <c r="K133">
         <v>6.138342462787552</v>
@@ -8123,10 +7859,8 @@
           <t>0.624</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>15.929535230769229</t>
-        </is>
+      <c r="J134">
+        <v>15.92953523076923</v>
       </c>
       <c r="K134">
         <v>6.637306346153846</v>
@@ -8181,10 +7915,8 @@
           <t>0.81299999999999994</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>14.45565276923077</t>
-        </is>
+      <c r="J135">
+        <v>14.45565276923077</v>
       </c>
       <c r="K135">
         <v>4.622963985239853</v>
@@ -8239,10 +7971,8 @@
           <t>0.59899999999999998</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>9.7721160000000005</t>
-        </is>
+      <c r="J136">
+        <v>9.772116</v>
       </c>
       <c r="K136">
         <v>4.241653021702838</v>
@@ -8297,10 +8027,8 @@
           <t>0.64200000000000002</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>11.389469538461539</t>
-        </is>
+      <c r="J137">
+        <v>11.38946953846154</v>
       </c>
       <c r="K137">
         <v>4.612557757009346</v>
@@ -8355,10 +8083,8 @@
           <t>0.72099999999999997</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>13.318485230769229</t>
-        </is>
+      <c r="J138">
+        <v>13.31848523076923</v>
       </c>
       <c r="K138">
         <v>4.802782468793342</v>
@@ -8413,10 +8139,8 @@
           <t>0.63900000000000001</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>11.798585538461538</t>
-        </is>
+      <c r="J139">
+        <v>11.79858553846154</v>
       </c>
       <c r="K139">
         <v>4.800676431924883</v>
@@ -8471,10 +8195,8 @@
           <t>0.69799999999999995</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>17.441543538461538</t>
-        </is>
+      <c r="J140">
+        <v>17.44154353846154</v>
       </c>
       <c r="K140">
         <v>6.496850028653295</v>
@@ -8529,10 +8251,8 @@
           <t>0.72099999999999997</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>13.670079692307691</t>
-        </is>
+      <c r="J141">
+        <v>13.67007969230769</v>
       </c>
       <c r="K141">
         <v>4.929571040221914</v>
@@ -8587,10 +8307,8 @@
           <t>0.79200000000000004</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>19.884925384615386</t>
-        </is>
+      <c r="J142">
+        <v>19.88492538461539</v>
       </c>
       <c r="K142">
         <v>6.527879545454546</v>
@@ -8645,10 +8363,8 @@
           <t>0.86899999999999999</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>17.002193076923078</t>
-        </is>
+      <c r="J143">
+        <v>17.00219307692308</v>
       </c>
       <c r="K143">
         <v>5.086962255466053</v>
@@ -8703,10 +8419,8 @@
           <t>0.53600000000000003</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>12.090566769230769</t>
-        </is>
+      <c r="J144">
+        <v>12.09056676923077</v>
       </c>
       <c r="K144">
         <v>5.864827164179104</v>
@@ -8761,10 +8475,8 @@
           <t>0.70599999999999996</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>14.71088676923077</t>
-        </is>
+      <c r="J145">
+        <v>14.71088676923077</v>
       </c>
       <c r="K145">
         <v>5.417607025495752</v>
@@ -8819,10 +8531,8 @@
           <t>0.65100000000000002</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>13.021512461538462</t>
-        </is>
+      <c r="J146">
+        <v>13.02151246153846</v>
       </c>
       <c r="K146">
         <v>5.200604055299539</v>
@@ -8877,10 +8587,8 @@
           <t>0.58299999999999996</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>15.135024923076921</t>
-        </is>
+      <c r="J147">
+        <v>15.13502492307692</v>
       </c>
       <c r="K147">
         <v>6.749753825042881</v>
@@ -8935,10 +8643,8 @@
           <t>0.64300000000000002</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>13.940335846153847</t>
-        </is>
+      <c r="J148">
+        <v>13.94033584615385</v>
       </c>
       <c r="K148">
         <v>5.636838755832037</v>
@@ -8993,10 +8699,8 @@
           <t>0.79100000000000004</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>15.869399076923075</t>
-        </is>
+      <c r="J149">
+        <v>15.86939907692308</v>
       </c>
       <c r="K149">
         <v>5.216237370417193</v>
@@ -9051,10 +8755,8 @@
           <t>8.7999999999999995E-2</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>14.494872000000001</t>
-        </is>
+      <c r="J150">
+        <v>14.494872</v>
       </c>
       <c r="K150">
         <v>42.82575818181819</v>
@@ -9109,10 +8811,8 @@
           <t>0.81499999999999995</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>15.445118307692308</t>
-        </is>
+      <c r="J151">
+        <v>15.44511830769231</v>
       </c>
       <c r="K151">
         <v>4.92727700613497</v>
@@ -9167,10 +8867,8 @@
           <t>8.4000000000000005E-2</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>7.5189355384615375</t>
-        </is>
+      <c r="J152">
+        <v>7.518935538461538</v>
       </c>
       <c r="K152">
         <v>23.27289571428571</v>
@@ -9225,10 +8923,8 @@
           <t>0.14499999999999999</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>16.177020461538461</t>
-        </is>
+      <c r="J153">
+        <v>16.17702046153846</v>
       </c>
       <c r="K153">
         <v>29.0070711724138</v>
@@ -9283,10 +8979,8 @@
           <t>0.13400000000000001</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>11.730510461538461</t>
-        </is>
+      <c r="J154">
+        <v>11.73051046153846</v>
       </c>
       <c r="K154">
         <v>22.76069194029851</v>
@@ -9341,10 +9035,8 @@
           <t>0.11</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>13.684198615384613</t>
-        </is>
+      <c r="J155">
+        <v>13.68419861538461</v>
       </c>
       <c r="K155">
         <v>32.34446945454545</v>
@@ -9399,10 +9091,8 @@
           <t>0.14499999999999999</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>9.7777255384615387</t>
-        </is>
+      <c r="J156">
+        <v>9.777725538461539</v>
       </c>
       <c r="K156">
         <v>17.53247337931035</v>
@@ -9457,10 +9147,8 @@
           <t>0.13400000000000001</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>15.224920153846153</t>
-        </is>
+      <c r="J157">
+        <v>15.22492015384615</v>
       </c>
       <c r="K157">
         <v>29.54088985074627</v>
@@ -9515,10 +9203,8 @@
           <t>0.13800000000000001</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>13.55175646153846</t>
-        </is>
+      <c r="J158">
+        <v>13.55175646153846</v>
       </c>
       <c r="K158">
         <v>25.53229478260869</v>
@@ -9573,10 +9259,8 @@
           <t>0.16600000000000001</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>17.085908307692304</t>
-        </is>
+      <c r="J159">
+        <v>17.0859083076923</v>
       </c>
       <c r="K159">
         <v>26.76106120481927</v>
@@ -9631,10 +9315,8 @@
           <t>9.9000000000000005E-2</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>13.027930153846153</t>
-        </is>
+      <c r="J160">
+        <v>13.02793015384615</v>
       </c>
       <c r="K160">
         <v>34.21476606060606</v>
@@ -9689,10 +9371,8 @@
           <t>0.16800000000000001</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>11.514400615384616</t>
-        </is>
+      <c r="J161">
+        <v>11.51440061538462</v>
       </c>
       <c r="K161">
         <v>17.81990571428571</v>
@@ -9747,10 +9427,8 @@
           <t>0.22</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>14.040404307692308</t>
-        </is>
+      <c r="J162">
+        <v>14.04040430769231</v>
       </c>
       <c r="K162">
         <v>16.59320509090909</v>
@@ -9805,10 +9483,8 @@
           <t>0.13500000000000001</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>17.18127046153846</t>
-        </is>
+      <c r="J163">
+        <v>17.18127046153846</v>
       </c>
       <c r="K163">
         <v>33.08985422222222</v>
@@ -9863,10 +9539,8 @@
           <t>0.108</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>17.090376923076921</t>
-        </is>
+      <c r="J164">
+        <v>17.09037692307692</v>
       </c>
       <c r="K164">
         <v>41.1435</v>
@@ -9921,10 +9595,8 @@
           <t>0.13700000000000001</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>12.570467538461536</t>
-        </is>
+      <c r="J165">
+        <v>12.57046753846154</v>
       </c>
       <c r="K165">
         <v>23.85636175182481</v>
@@ -9979,10 +9651,8 @@
           <t>0.11799999999999999</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>20.21945353846154</t>
-        </is>
+      <c r="J166">
+        <v>20.21945353846154</v>
       </c>
       <c r="K166">
         <v>44.55133830508475</v>
@@ -10037,10 +9707,8 @@
           <t>0.14199999999999999</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>16.018669846153848</t>
-        </is>
+      <c r="J167">
+        <v>16.01866984615385</v>
       </c>
       <c r="K167">
         <v>29.32995887323944</v>
@@ -10095,10 +9763,8 @@
           <t>0.126</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>14.606777538461538</t>
-        </is>
+      <c r="J168">
+        <v>14.60677753846154</v>
       </c>
       <c r="K168">
         <v>30.14096952380952</v>
@@ -10153,10 +9819,8 @@
           <t>0.127</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>14.921196923076922</t>
-        </is>
+      <c r="J169">
+        <v>14.92119692307692</v>
       </c>
       <c r="K169">
         <v>30.54733228346456</v>
@@ -10211,10 +9875,8 @@
           <t>0.17199999999999999</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>21.675699230769233</t>
-        </is>
+      <c r="J170">
+        <v>21.67569923076923</v>
       </c>
       <c r="K170">
         <v>32.76559186046512</v>
@@ -10269,10 +9931,8 @@
           <t>0.156</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>15.427148769230767</t>
-        </is>
+      <c r="J171">
+        <v>15.42714876923077</v>
       </c>
       <c r="K171">
         <v>25.71191461538461</v>
@@ -10327,10 +9987,8 @@
           <t>0.14099999999999999</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>14.86667030769231</t>
-        </is>
+      <c r="J172">
+        <v>14.86667030769231</v>
       </c>
       <c r="K172">
         <v>27.41371829787235</v>
@@ -10385,10 +10043,8 @@
           <t>0.13</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>14.720537076923076</t>
-        </is>
+      <c r="J173">
+        <v>14.72053707692308</v>
       </c>
       <c r="K173">
         <v>29.44107415384615</v>
@@ -10443,10 +10099,8 @@
           <t>0.183</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>10.955538461538461</t>
-        </is>
+      <c r="J174">
+        <v>10.95553846153846</v>
       </c>
       <c r="K174">
         <v>15.56524590163935</v>
@@ -10501,10 +10155,8 @@
           <t>0.14199999999999999</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>13.816735846153845</t>
-        </is>
+      <c r="J175">
+        <v>13.81673584615385</v>
       </c>
       <c r="K175">
         <v>25.29824873239437</v>
@@ -10559,10 +10211,8 @@
           <t>0.13800000000000001</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>13.186993846153843</t>
-        </is>
+      <c r="J176">
+        <v>13.18699384615384</v>
       </c>
       <c r="K176">
         <v>24.84506086956521</v>
@@ -10617,10 +10267,8 @@
           <t>0.20699999999999999</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>14.685120923076923</t>
-        </is>
+      <c r="J177">
+        <v>14.68512092307692</v>
       </c>
       <c r="K177">
         <v>18.44507942028986</v>
@@ -10675,10 +10323,8 @@
           <t>0.40400000000000003</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>8.3622203076923061</t>
-        </is>
+      <c r="J178">
+        <v>8.362220307692306</v>
       </c>
       <c r="K178">
         <v>5.381626930693069</v>
@@ -10733,10 +10379,8 @@
           <t>0.27900000000000003</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>8.927785384615385</t>
-        </is>
+      <c r="J179">
+        <v>8.927785384615385</v>
       </c>
       <c r="K179">
         <v>8.319799999999999</v>
@@ -10791,10 +10435,8 @@
           <t>0.39700000000000002</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>10.439033076923076</t>
-        </is>
+      <c r="J180">
+        <v>10.43903307692308</v>
       </c>
       <c r="K180">
         <v>6.836646347607052</v>
@@ -10849,10 +10491,8 @@
           <t>0.41399999999999998</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>10.293137538461538</t>
-        </is>
+      <c r="J181">
+        <v>10.29313753846154</v>
       </c>
       <c r="K181">
         <v>6.464289275362319</v>
@@ -10907,10 +10547,8 @@
           <t>0.34200000000000003</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>6.5195819999999998</t>
-        </is>
+      <c r="J182">
+        <v>6.519582</v>
       </c>
       <c r="K182">
         <v>4.956407368421052</v>
@@ -10965,10 +10603,8 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>7.9323300000000003</t>
-        </is>
+      <c r="J183">
+        <v>7.93233</v>
       </c>
       <c r="K183">
         <v>3.437343</v>
@@ -11023,10 +10659,8 @@
           <t>0.36599999999999999</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>8.6053795384615359</t>
-        </is>
+      <c r="J184">
+        <v>8.605379538461536</v>
       </c>
       <c r="K184">
         <v>6.113111147540983</v>
@@ -11081,10 +10715,8 @@
           <t>0.38800000000000001</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>6.0465743076923077</t>
-        </is>
+      <c r="J185">
+        <v>6.046574307692308</v>
       </c>
       <c r="K185">
         <v>4.051828144329897</v>
@@ -11139,10 +10771,8 @@
           <t>0.22600000000000001</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>4.134244615384616</t>
-        </is>
+      <c r="J186">
+        <v>4.134244615384616</v>
       </c>
       <c r="K186">
         <v>4.756210619469027</v>
@@ -11197,10 +10827,8 @@
           <t>0.48299999999999998</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>8.830521692307693</t>
-        </is>
+      <c r="J187">
+        <v>8.830521692307693</v>
       </c>
       <c r="K187">
         <v>4.753489937888199</v>
@@ -11255,10 +10883,8 @@
           <t>0.51900000000000002</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>11.013297692307692</t>
-        </is>
+      <c r="J188">
+        <v>11.01329769230769</v>
       </c>
       <c r="K188">
         <v>5.517258959537572</v>
@@ -11313,10 +10939,8 @@
           <t>0.27700000000000002</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>12.59509246153846</t>
-        </is>
+      <c r="J189">
+        <v>12.59509246153846</v>
       </c>
       <c r="K189">
         <v>11.82210844765343</v>
@@ -11371,10 +10995,8 @@
           <t>0.33600000000000002</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>21.190997076923075</t>
-        </is>
+      <c r="J190">
+        <v>21.19099707692308</v>
       </c>
       <c r="K190">
         <v>16.39779535714285</v>
@@ -11429,10 +11051,8 @@
           <t>0.37</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>10.710667846153845</t>
-        </is>
+      <c r="J191">
+        <v>10.71066784615384</v>
       </c>
       <c r="K191">
         <v>7.526415243243243</v>
@@ -11487,10 +11107,8 @@
           <t>0.46300000000000002</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>14.883308769230768</t>
-        </is>
+      <c r="J192">
+        <v>14.88330876923077</v>
       </c>
       <c r="K192">
         <v>8.35779758099352</v>
@@ -11545,10 +11163,8 @@
           <t>0.38200000000000001</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>21.759129230769233</t>
-        </is>
+      <c r="J193">
+        <v>21.75912923076923</v>
       </c>
       <c r="K193">
         <v>14.80987853403141</v>
@@ -11603,10 +11219,8 @@
           <t>0.624</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>15.42886015384615</t>
-        </is>
+      <c r="J194">
+        <v>15.42886015384615</v>
       </c>
       <c r="K194">
         <v>6.428691730769229</v>
@@ -11661,10 +11275,8 @@
           <t>0.32600000000000001</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>11.836140923076918</t>
-        </is>
+      <c r="J195">
+        <v>11.83614092307692</v>
       </c>
       <c r="K195">
         <v>9.439866993865028</v>
@@ -11719,10 +11331,8 @@
           <t>0.59299999999999997</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>20.389546153846151</t>
-        </is>
+      <c r="J196">
+        <v>20.38954615384615</v>
       </c>
       <c r="K196">
         <v>8.939767284991568</v>
@@ -11777,10 +11387,8 @@
           <t>0.247</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>11.656683230769231</t>
-        </is>
+      <c r="J197">
+        <v>11.65668323076923</v>
       </c>
       <c r="K197">
         <v>12.27019287449393</v>
@@ -11835,10 +11443,8 @@
           <t>0.50600000000000001</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>14.315271692307691</t>
-        </is>
+      <c r="J198">
+        <v>14.31527169230769</v>
       </c>
       <c r="K198">
         <v>7.355673201581028</v>
@@ -11893,10 +11499,8 @@
           <t>0.435</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>10.224064153846154</t>
-        </is>
+      <c r="J199">
+        <v>10.22406415384615</v>
       </c>
       <c r="K199">
         <v>6.110934896551724</v>
@@ -11951,10 +11555,8 @@
           <t>0.45800000000000002</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>13.847208</t>
-        </is>
+      <c r="J200">
+        <v>13.847208</v>
       </c>
       <c r="K200">
         <v>7.860860436681222</v>
@@ -12009,10 +11611,8 @@
           <t>0.37</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>10.759775076923077</t>
-        </is>
+      <c r="J201">
+        <v>10.75977507692308</v>
       </c>
       <c r="K201">
         <v>7.560923027027028</v>
@@ -12067,10 +11667,8 @@
           <t>0.40899999999999997</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>11.858483999999999</t>
-        </is>
+      <c r="J202">
+        <v>11.858484</v>
       </c>
       <c r="K202">
         <v>7.538400586797066</v>
@@ -12125,10 +11723,8 @@
           <t>0.42799999999999999</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>10.897731692307692</t>
-        </is>
+      <c r="J203">
+        <v>10.89773169230769</v>
       </c>
       <c r="K203">
         <v>6.62011738317757</v>
@@ -12183,10 +11779,8 @@
           <t>0.16800000000000001</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>10.418021076923075</t>
-        </is>
+      <c r="J204">
+        <v>10.41802107692308</v>
       </c>
       <c r="K204">
         <v>16.12312785714285</v>
@@ -12241,10 +11835,8 @@
           <t>0.57099999999999995</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>15.150712615384613</t>
-        </is>
+      <c r="J205">
+        <v>15.15071261538461</v>
       </c>
       <c r="K205">
         <v>6.898748301225919</v>
@@ -12299,10 +11891,8 @@
           <t>0.64400000000000002</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>17.886408461538462</t>
-        </is>
+      <c r="J206">
+        <v>17.88640846153846</v>
       </c>
       <c r="K206">
         <v>7.221220807453417</v>
@@ -12357,10 +11947,8 @@
           <t>0.43099999999999999</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>12.221677846153845</t>
-        </is>
+      <c r="J207">
+        <v>12.22167784615385</v>
       </c>
       <c r="K207">
         <v>7.372705893271462</v>
@@ -12415,10 +12003,8 @@
           <t>0.48899999999999999</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>13.680965999999998</t>
-        </is>
+      <c r="J208">
+        <v>13.680966</v>
       </c>
       <c r="K208">
         <v>7.274133251533741</v>
@@ -12473,10 +12059,8 @@
           <t>0.60699999999999998</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>17.054247692307694</t>
-        </is>
+      <c r="J209">
+        <v>17.05424769230769</v>
       </c>
       <c r="K209">
         <v>7.304949588138387</v>
@@ -12531,10 +12115,8 @@
           <t>0.51300000000000001</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>18.039815076923073</t>
-        </is>
+      <c r="J210">
+        <v>18.03981507692307</v>
       </c>
       <c r="K210">
         <v>9.142986198830409</v>
@@ -12589,10 +12171,8 @@
           <t>0.54100000000000004</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>8.7759</t>
-        </is>
+      <c r="J211">
+        <v>8.7759</v>
       </c>
       <c r="K211">
         <v>4.21762292051756</v>
@@ -12647,10 +12227,8 @@
           <t>0.52800000000000002</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>16.780996615384616</t>
-        </is>
+      <c r="J212">
+        <v>16.78099661538462</v>
       </c>
       <c r="K212">
         <v>8.263369545454545</v>
@@ -12705,10 +12283,8 @@
           <t>0.627</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>12.985620923076924</t>
-        </is>
+      <c r="J213">
+        <v>12.98562092307692</v>
       </c>
       <c r="K213">
         <v>5.384786985645934</v>
@@ -12763,10 +12339,8 @@
           <t>0.60799999999999998</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>13.504835999999999</t>
-        </is>
+      <c r="J214">
+        <v>13.504836</v>
       </c>
       <c r="K214">
         <v>5.775094342105263</v>
@@ -12821,10 +12395,8 @@
           <t>0.67400000000000004</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>15.375712153846152</t>
-        </is>
+      <c r="J215">
+        <v>15.37571215384615</v>
       </c>
       <c r="K215">
         <v>5.931283620178041</v>
@@ -12879,10 +12451,8 @@
           <t>0.79900000000000004</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>17.188829076923078</t>
-        </is>
+      <c r="J216">
+        <v>17.18882907692308</v>
       </c>
       <c r="K216">
         <v>5.593361151439299</v>
@@ -12937,10 +12507,8 @@
           <t>0.73</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>22.324456615384616</t>
-        </is>
+      <c r="J217">
+        <v>22.32445661538462</v>
       </c>
       <c r="K217">
         <v>7.951176328767124</v>
@@ -12995,10 +12563,8 @@
           <t>0.63600000000000001</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>23.885382000000003</t>
-        </is>
+      <c r="J218">
+        <v>23.885382</v>
       </c>
       <c r="K218">
         <v>9.764464339622643</v>
@@ -13053,10 +12619,8 @@
           <t>0.629</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>13.270328769230767</t>
-        </is>
+      <c r="J219">
+        <v>13.27032876923077</v>
       </c>
       <c r="K219">
         <v>5.485350524642289</v>
@@ -13111,10 +12675,8 @@
           <t>0.58299999999999996</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>20.50962830769231</t>
-        </is>
+      <c r="J220">
+        <v>20.50962830769231</v>
       </c>
       <c r="K220">
         <v>9.146660994854203</v>
@@ -13169,10 +12731,8 @@
           <t>0.64300000000000002</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>23.063346923076924</t>
-        </is>
+      <c r="J221">
+        <v>23.06334692307692</v>
       </c>
       <c r="K221">
         <v>9.325770139968895</v>
@@ -13227,10 +12787,8 @@
           <t>0.57399999999999995</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>16.360994307692309</t>
-        </is>
+      <c r="J222">
+        <v>16.36099430769231</v>
       </c>
       <c r="K222">
         <v>7.410903344947736</v>
@@ -13285,10 +12843,8 @@
           <t>0.76200000000000001</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>12.441400615384614</t>
-        </is>
+      <c r="J223">
+        <v>12.44140061538461</v>
       </c>
       <c r="K223">
         <v>4.245097322834646</v>
@@ -13343,10 +12899,8 @@
           <t>0.56000000000000005</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>14.774065384615383</t>
-        </is>
+      <c r="J224">
+        <v>14.77406538461538</v>
       </c>
       <c r="K224">
         <v>6.859387499999999</v>
@@ -13401,10 +12955,8 @@
           <t>0.53800000000000003</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>16.241672769230767</t>
-        </is>
+      <c r="J225">
+        <v>16.24167276923077</v>
       </c>
       <c r="K225">
         <v>7.849135539033456</v>
@@ -13459,10 +13011,8 @@
           <t>0.58199999999999996</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>15.705771692307691</t>
-        </is>
+      <c r="J226">
+        <v>15.70577169230769</v>
       </c>
       <c r="K226">
         <v>7.01632412371134</v>
@@ -13517,10 +13067,8 @@
           <t>0.74399999999999999</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>12.359396769230772</t>
-        </is>
+      <c r="J227">
+        <v>12.35939676923077</v>
       </c>
       <c r="K227">
         <v>4.319144032258065</v>
@@ -13575,10 +13123,8 @@
           <t>0.4</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>13.562595230769229</t>
-        </is>
+      <c r="J228">
+        <v>13.56259523076923</v>
       </c>
       <c r="K228">
         <v>8.815686899999999</v>
@@ -13633,10 +13179,8 @@
           <t>0.72499999999999998</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>20.496269999999996</t>
-        </is>
+      <c r="J229">
+        <v>20.49627</v>
       </c>
       <c r="K229">
         <v>7.35038648275862</v>
@@ -13691,10 +13235,8 @@
           <t>0.50700000000000001</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>20.046223384615384</t>
-        </is>
+      <c r="J230">
+        <v>20.04622338461538</v>
       </c>
       <c r="K230">
         <v>10.28011455621302</v>
@@ -13749,10 +13291,8 @@
           <t>0.55000000000000004</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>22.369047692307689</t>
-        </is>
+      <c r="J231">
+        <v>22.36904769230769</v>
       </c>
       <c r="K231">
         <v>10.57445890909091</v>
@@ -13807,10 +13347,8 @@
           <t>0.46200000000000002</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>7.0538192307692311</t>
-        </is>
+      <c r="J232">
+        <v>7.053819230769231</v>
       </c>
       <c r="K232">
         <v>3.969681818181818</v>
@@ -13865,10 +13403,8 @@
           <t>0.60299999999999998</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>27.549028615384618</t>
-        </is>
+      <c r="J233">
+        <v>27.54902861538462</v>
       </c>
       <c r="K233">
         <v>11.87851980099503</v>
@@ -13923,10 +13459,8 @@
           <t>0.61499999999999999</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>21.042724615384614</t>
-        </is>
+      <c r="J234">
+        <v>21.04272461538461</v>
       </c>
       <c r="K234">
         <v>8.896111219512195</v>
@@ -13981,10 +13515,8 @@
           <t>0.183</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>16.103525999999999</t>
-        </is>
+      <c r="J235">
+        <v>16.103526</v>
       </c>
       <c r="K235">
         <v>22.87932655737705</v>
@@ -14039,10 +13571,8 @@
           <t>0.105</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>17.109344769230766</t>
-        </is>
+      <c r="J236">
+        <v>17.10934476923077</v>
       </c>
       <c r="K236">
         <v>42.36599657142857</v>
@@ -14097,10 +13627,8 @@
           <t>0.252</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>21.846362307692306</t>
-        </is>
+      <c r="J237">
+        <v>21.84636230769231</v>
       </c>
       <c r="K237">
         <v>22.53989761904762</v>
@@ -14155,10 +13683,8 @@
           <t>0.32100000000000001</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>22.433129538461536</t>
-        </is>
+      <c r="J238">
+        <v>22.43312953846154</v>
       </c>
       <c r="K238">
         <v>18.17013607476635</v>
@@ -14213,10 +13739,8 @@
           <t>0.29499999999999998</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>12.115191692307691</t>
-        </is>
+      <c r="J239">
+        <v>12.11519169230769</v>
       </c>
       <c r="K239">
         <v>10.67779606779661</v>
@@ -14271,10 +13795,8 @@
           <t>0.123</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>17.497876615384612</t>
-        </is>
+      <c r="J240">
+        <v>17.49787661538461</v>
       </c>
       <c r="K240">
         <v>36.98738146341463</v>
@@ -14329,10 +13851,8 @@
           <t>0.505</t>
         </is>
       </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>12.803025692307694</t>
-        </is>
+      <c r="J241">
+        <v>12.80302569230769</v>
       </c>
       <c r="K241">
         <v>6.591656792079209</v>
@@ -14387,10 +13907,8 @@
           <t>0.29499999999999998</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>18.869028461538459</t>
-        </is>
+      <c r="J242">
+        <v>18.86902846153846</v>
       </c>
       <c r="K242">
         <v>16.63033016949153</v>
@@ -14445,10 +13963,8 @@
           <t>0.28499999999999998</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>11.476084615384616</t>
-        </is>
+      <c r="J243">
+        <v>11.47608461538462</v>
       </c>
       <c r="K243">
         <v>10.46941052631579</v>
@@ -14503,10 +14019,8 @@
           <t>0.28100000000000003</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>11.073053538461537</t>
-        </is>
+      <c r="J244">
+        <v>11.07305353846154</v>
       </c>
       <c r="K244">
         <v>10.24552996441281</v>
@@ -14561,10 +14075,8 @@
           <t>7.3999999999999996E-2</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>9.9100250769230769</t>
-        </is>
+      <c r="J245">
+        <v>9.910025076923077</v>
       </c>
       <c r="K245">
         <v>34.81900702702703</v>
@@ -14619,10 +14131,8 @@
           <t>0.153</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>7.7714598461538449</t>
-        </is>
+      <c r="J246">
+        <v>7.771459846153845</v>
       </c>
       <c r="K246">
         <v>13.20640235294118</v>
@@ -14677,10 +14187,8 @@
           <t>0.112</t>
         </is>
       </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>16.953561230769232</t>
-        </is>
+      <c r="J247">
+        <v>16.95356123076923</v>
       </c>
       <c r="K247">
         <v>39.35648142857143</v>
@@ -14735,10 +14243,8 @@
           <t>9.2999999999999999E-2</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>15.719367692307692</t>
-        </is>
+      <c r="J248">
+        <v>15.71936769230769</v>
       </c>
       <c r="K248">
         <v>43.94661935483871</v>
@@ -14793,10 +14299,8 @@
           <t>7.1999999999999995E-2</t>
         </is>
       </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>10.536867230769229</t>
-        </is>
+      <c r="J249">
+        <v>10.53686723076923</v>
       </c>
       <c r="K249">
         <v>38.04979833333334</v>
@@ -14851,10 +14355,8 @@
           <t>0.11899999999999999</t>
         </is>
       </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>21.262447384615381</t>
-        </is>
+      <c r="J250">
+        <v>21.26244738461538</v>
       </c>
       <c r="K250">
         <v>46.45576739495798</v>
@@ -14909,10 +14411,8 @@
           <t>0.27400000000000002</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>13.011624461538462</t>
-        </is>
+      <c r="J251">
+        <v>13.01162446153846</v>
       </c>
       <c r="K251">
         <v>12.34679693430657</v>
@@ -14967,10 +14467,8 @@
           <t>0.41599999999999998</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>10.775557846153845</t>
-        </is>
+      <c r="J252">
+        <v>10.77555784615384</v>
       </c>
       <c r="K252">
         <v>6.734723653846154</v>
@@ -15025,10 +14523,8 @@
           <t>0.314</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>11.142459692307693</t>
-        </is>
+      <c r="J253">
+        <v>11.14245969230769</v>
       </c>
       <c r="K253">
         <v>9.226240509554142</v>
@@ -15083,10 +14579,8 @@
           <t>0.433</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>11.72219123076923</t>
-        </is>
+      <c r="J254">
+        <v>11.72219123076923</v>
       </c>
       <c r="K254">
         <v>7.038729145496536</v>
@@ -15141,10 +14635,8 @@
           <t>0.23300000000000001</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>11.885200615384614</t>
-        </is>
+      <c r="J255">
+        <v>11.88520061538461</v>
       </c>
       <c r="K255">
         <v>13.26245562231759</v>
@@ -15199,10 +14691,8 @@
           <t>0.25</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>11.72342723076923</t>
-        </is>
+      <c r="J256">
+        <v>11.72342723076923</v>
       </c>
       <c r="K256">
         <v>12.19236432</v>
@@ -15257,10 +14747,8 @@
           <t>0.49399999999999999</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>8.8419784615384618</t>
-        </is>
+      <c r="J257">
+        <v>8.841978461538462</v>
       </c>
       <c r="K257">
         <v>4.653672874493927</v>
@@ -15315,10 +14803,8 @@
           <t>0.186</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>12.513373846153845</t>
-        </is>
+      <c r="J258">
+        <v>12.51337384615385</v>
       </c>
       <c r="K258">
         <v>17.49181290322581</v>
@@ -15373,10 +14859,8 @@
           <t>0.32200000000000001</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>13.997286923076921</t>
-        </is>
+      <c r="J259">
+        <v>13.99728692307692</v>
       </c>
       <c r="K259">
         <v>11.30215714285714</v>
@@ -15431,10 +14915,8 @@
           <t>0.47899999999999998</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>7.242261692307693</t>
-        </is>
+      <c r="J260">
+        <v>7.242261692307693</v>
       </c>
       <c r="K260">
         <v>3.931081503131525</v>
@@ -15489,10 +14971,8 @@
           <t>0.23599999999999999</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>9.405404307692308</t>
-        </is>
+      <c r="J261">
+        <v>9.405404307692308</v>
       </c>
       <c r="K261">
         <v>10.36188610169492</v>
@@ -15547,10 +15027,8 @@
           <t>0.31900000000000001</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>13.857048461538461</t>
-        </is>
+      <c r="J262">
+        <v>13.85704846153846</v>
       </c>
       <c r="K262">
         <v>11.2941460815047</v>
@@ -15605,10 +15083,8 @@
           <t>0.26700000000000002</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>13.126049538461539</t>
-        </is>
+      <c r="J263">
+        <v>13.12604953846154</v>
       </c>
       <c r="K263">
         <v>12.78192089887641</v>
@@ -15663,10 +15139,8 @@
           <t>0.216</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>13.443653999999999</t>
-        </is>
+      <c r="J264">
+        <v>13.443654</v>
       </c>
       <c r="K264">
         <v>16.18217611111111</v>
@@ -15721,10 +15195,8 @@
           <t>0.20499999999999999</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>15.516283384615383</t>
-        </is>
+      <c r="J265">
+        <v>15.51628338461538</v>
       </c>
       <c r="K265">
         <v>19.67918868292683</v>
@@ -15779,10 +15251,8 @@
           <t>0.36099999999999999</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>15.553838769230767</t>
-        </is>
+      <c r="J266">
+        <v>15.55383876923077</v>
       </c>
       <c r="K266">
         <v>11.20221074792244</v>
@@ -15837,10 +15307,8 @@
           <t>0.27300000000000002</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>12.289039846153846</t>
-        </is>
+      <c r="J267">
+        <v>12.28903984615385</v>
       </c>
       <c r="K267">
         <v>11.70384747252747</v>
@@ -15895,10 +15363,8 @@
           <t>0.33100000000000002</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>9.7916067692307696</t>
-        </is>
+      <c r="J268">
+        <v>9.79160676923077</v>
       </c>
       <c r="K268">
         <v>7.691292326283988</v>
@@ -15953,10 +15419,8 @@
           <t>0.29599999999999999</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>11.019572769230768</t>
-        </is>
+      <c r="J269">
+        <v>11.01957276923077</v>
       </c>
       <c r="K269">
         <v>9.679354459459459</v>
@@ -16011,10 +15475,8 @@
           <t>0.25900000000000001</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>13.574527384615386</t>
-        </is>
+      <c r="J270">
+        <v>13.57452738461539</v>
       </c>
       <c r="K270">
         <v>13.62693868725869</v>
@@ -16069,10 +15531,8 @@
           <t>0.309</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>11.077902461538459</t>
-        </is>
+      <c r="J271">
+        <v>11.07790246153846</v>
       </c>
       <c r="K271">
         <v>9.321212427184465</v>
@@ -16127,10 +15587,8 @@
           <t>0.28599999999999998</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>9.1944761538461535</t>
-        </is>
+      <c r="J272">
+        <v>9.194476153846153</v>
       </c>
       <c r="K272">
         <v>8.358614685314686</v>
@@ -16185,10 +15643,8 @@
           <t>0.34699999999999998</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>11.017195846153845</t>
-        </is>
+      <c r="J273">
+        <v>11.01719584615384</v>
       </c>
       <c r="K273">
         <v>8.254959423631123</v>
@@ -16243,10 +15699,8 @@
           <t>0.29799999999999999</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>11.248375384615382</t>
-        </is>
+      <c r="J274">
+        <v>11.24837538461538</v>
       </c>
       <c r="K274">
         <v>9.814018791946308</v>
@@ -16301,10 +15755,8 @@
           <t>0.371</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>12.545747538461539</t>
-        </is>
+      <c r="J275">
+        <v>12.54574753846154</v>
       </c>
       <c r="K275">
         <v>8.792168086253371</v>
@@ -16359,10 +15811,8 @@
           <t>0.28999999999999998</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>11.41533046153846</t>
-        </is>
+      <c r="J276">
+        <v>11.41533046153846</v>
       </c>
       <c r="K276">
         <v>10.23443420689655</v>
@@ -16417,10 +15867,8 @@
           <t>0.29899999999999999</t>
         </is>
       </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>13.207625538461535</t>
-        </is>
+      <c r="J277">
+        <v>13.20762553846154</v>
       </c>
       <c r="K277">
         <v>11.48489177257525</v>
@@ -16475,10 +15923,8 @@
           <t>0.307</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>14.832300000000002</t>
-        </is>
+      <c r="J278">
+        <v>14.8323</v>
       </c>
       <c r="K278">
         <v>12.56155700325733</v>
@@ -16533,10 +15979,8 @@
           <t>0.249</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>12.805973076923079</t>
-        </is>
+      <c r="J279">
+        <v>12.80597307692308</v>
       </c>
       <c r="K279">
         <v>13.37169879518073</v>
@@ -16591,10 +16035,8 @@
           <t>0.26600000000000001</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>10.542524307692307</t>
-        </is>
+      <c r="J280">
+        <v>10.54252430769231</v>
       </c>
       <c r="K280">
         <v>10.3047230075188</v>
@@ -16649,10 +16091,8 @@
           <t>0.23599999999999999</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t>6.5989236923076922</t>
-        </is>
+      <c r="J281">
+        <v>6.598923692307692</v>
       </c>
       <c r="K281">
         <v>7.270000677966102</v>
@@ -16707,10 +16147,8 @@
           <t>0.29399999999999998</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>12.839345076923076</t>
-        </is>
+      <c r="J282">
+        <v>12.83934507692308</v>
       </c>
       <c r="K282">
         <v>11.35452285714286</v>
@@ -16765,10 +16203,8 @@
           <t>0.32400000000000001</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>14.648326153846154</t>
-        </is>
+      <c r="J283">
+        <v>14.64832615384615</v>
       </c>
       <c r="K283">
         <v>11.75482962962963</v>
@@ -16823,10 +16259,8 @@
           <t>0.312</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>12.503533384615384</t>
-        </is>
+      <c r="J284">
+        <v>12.50353338461538</v>
       </c>
       <c r="K284">
         <v>10.41961115384615</v>
@@ -16881,10 +16315,8 @@
           <t>0.31</t>
         </is>
       </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>11.862429692307693</t>
-        </is>
+      <c r="J285">
+        <v>11.86242969230769</v>
       </c>
       <c r="K285">
         <v>9.949134580645161</v>
@@ -16939,10 +16371,8 @@
           <t>0.28199999999999997</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>14.868762</t>
-        </is>
+      <c r="J286">
+        <v>14.868762</v>
       </c>
       <c r="K286">
         <v>13.70878765957447</v>
@@ -16997,10 +16427,8 @@
           <t>0.29199999999999998</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>11.438339076923077</t>
-        </is>
+      <c r="J287">
+        <v>11.43833907692308</v>
       </c>
       <c r="K287">
         <v>10.18482246575343</v>
@@ -17055,10 +16483,8 @@
           <t>0.307</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>17.374038923076924</t>
-        </is>
+      <c r="J288">
+        <v>17.37403892307692</v>
       </c>
       <c r="K288">
         <v>14.71416977198697</v>
@@ -17113,10 +16539,8 @@
           <t>0.26600000000000001</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>11.677219846153847</t>
-        </is>
+      <c r="J289">
+        <v>11.67721984615385</v>
       </c>
       <c r="K289">
         <v>11.41382390977444</v>
@@ -17171,10 +16595,8 @@
           <t>0.25</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>12.455424461538463</t>
-        </is>
+      <c r="J290">
+        <v>12.45542446153846</v>
       </c>
       <c r="K290">
         <v>12.95364144</v>
@@ -17229,10 +16651,8 @@
           <t>0.27700000000000002</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>12.421909846153849</t>
-        </is>
+      <c r="J291">
+        <v>12.42190984615385</v>
       </c>
       <c r="K291">
         <v>11.65955436823105</v>
@@ -17287,10 +16707,8 @@
           <t>0.32800000000000001</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>14.637725076923077</t>
-        </is>
+      <c r="J292">
+        <v>14.63772507692308</v>
       </c>
       <c r="K292">
         <v>11.60307475609756</v>
@@ -17345,10 +16763,8 @@
           <t>0.311</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t>13.164080307692307</t>
-        </is>
+      <c r="J293">
+        <v>13.16408030769231</v>
       </c>
       <c r="K293">
         <v>11.00534045016077</v>
@@ -17403,10 +16819,8 @@
           <t>0.317</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>16.187193692307691</t>
-        </is>
+      <c r="J294">
+        <v>16.18719369230769</v>
       </c>
       <c r="K294">
         <v>13.27656264984227</v>
@@ -17461,10 +16875,8 @@
           <t>0.32</t>
         </is>
       </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>11.775529384615384</t>
-        </is>
+      <c r="J295">
+        <v>11.77552938461538</v>
       </c>
       <c r="K295">
         <v>9.567617624999999</v>
@@ -17519,10 +16931,8 @@
           <t>0.32100000000000001</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>11.36745923076923</t>
-        </is>
+      <c r="J296">
+        <v>11.36745923076923</v>
       </c>
       <c r="K296">
         <v>9.207287850467289</v>
@@ -17577,10 +16987,8 @@
           <t>0.29199999999999998</t>
         </is>
       </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>14.247576923076922</t>
-        </is>
+      <c r="J297">
+        <v>14.24757692307692</v>
       </c>
       <c r="K297">
         <v>12.68619863013699</v>
@@ -17635,10 +17043,8 @@
           <t>0.35699999999999998</t>
         </is>
       </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>10.203479999999999</t>
-        </is>
+      <c r="J298">
+        <v>10.20348</v>
       </c>
       <c r="K298">
         <v>7.431105882352941</v>
@@ -17693,10 +17099,8 @@
           <t>0.32100000000000001</t>
         </is>
       </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>12.061140461538463</t>
-        </is>
+      <c r="J299">
+        <v>12.06114046153846</v>
       </c>
       <c r="K299">
         <v>9.769148037383179</v>
@@ -17751,10 +17155,8 @@
           <t>0.32200000000000001</t>
         </is>
       </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>11.38319446153846</t>
-        </is>
+      <c r="J300">
+        <v>11.38319446153846</v>
       </c>
       <c r="K300">
         <v>9.191399254658384</v>
@@ -17809,10 +17211,8 @@
           <t>0.29299999999999998</t>
         </is>
       </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>13.698269999999999</t>
-        </is>
+      <c r="J301">
+        <v>13.69827</v>
       </c>
       <c r="K301">
         <v>12.1554614334471</v>
@@ -17867,10 +17267,8 @@
           <t>0.29499999999999998</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>13.43562</t>
-        </is>
+      <c r="J302">
+        <v>13.43562</v>
       </c>
       <c r="K302">
         <v>11.84156338983051</v>
@@ -17925,10 +17323,8 @@
           <t>0.318</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>11.245142769230769</t>
-        </is>
+      <c r="J303">
+        <v>11.24514276923077</v>
       </c>
       <c r="K303">
         <v>9.194141886792453</v>
@@ -17983,10 +17379,8 @@
           <t>0.35099999999999998</t>
         </is>
       </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>13.759166769230772</t>
-        </is>
+      <c r="J304">
+        <v>13.75916676923077</v>
       </c>
       <c r="K304">
         <v>10.19197538461539</v>
@@ -18041,10 +17435,8 @@
           <t>0.26</t>
         </is>
       </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>12.199477384615385</t>
-        </is>
+      <c r="J305">
+        <v>12.19947738461538</v>
       </c>
       <c r="K305">
         <v>12.19947738461538</v>
@@ -18099,10 +17491,8 @@
           <t>0.314</t>
         </is>
       </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>17.202187384615385</t>
-        </is>
+      <c r="J306">
+        <v>17.20218738461539</v>
       </c>
       <c r="K306">
         <v>14.24384942675159</v>
@@ -18157,10 +17547,8 @@
           <t>0.32600000000000001</t>
         </is>
       </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>11.33532323076923</t>
-        </is>
+      <c r="J307">
+        <v>11.33532323076923</v>
       </c>
       <c r="K307">
         <v>9.040441840490796</v>
@@ -18215,10 +17603,8 @@
           <t>0.33700000000000002</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>9.2594136923076924</t>
-        </is>
+      <c r="J308">
+        <v>9.259413692307692</v>
       </c>
       <c r="K308">
         <v>7.143761305637982</v>
@@ -18273,10 +17659,8 @@
           <t>0.28499999999999998</t>
         </is>
       </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>14.766791999999999</t>
-        </is>
+      <c r="J309">
+        <v>14.766792</v>
       </c>
       <c r="K309">
         <v>13.47145936842105</v>
@@ -18331,10 +17715,8 @@
           <t>0.33900000000000002</t>
         </is>
       </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>16.204212461538461</t>
-        </is>
+      <c r="J310">
+        <v>16.20421246153846</v>
       </c>
       <c r="K310">
         <v>12.42800955752212</v>
@@ -18389,10 +17771,8 @@
           <t>0.57599999999999996</t>
         </is>
       </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>11.054133230769228</t>
-        </is>
+      <c r="J311">
+        <v>11.05413323076923</v>
       </c>
       <c r="K311">
         <v>4.989712916666666</v>
@@ -18447,10 +17827,8 @@
           <t>0.52600000000000002</t>
         </is>
       </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>10.51029323076923</t>
-        </is>
+      <c r="J312">
+        <v>10.51029323076923</v>
       </c>
       <c r="K312">
         <v>5.195201977186311</v>
@@ -18505,10 +17883,8 @@
           <t>0.28899999999999998</t>
         </is>
       </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>14.852884153846153</t>
-        </is>
+      <c r="J313">
+        <v>14.85288415384615</v>
       </c>
       <c r="K313">
         <v>13.36245633217993</v>
@@ -18563,10 +17939,8 @@
           <t>0.42199999999999999</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>17.753918769230765</t>
-        </is>
+      <c r="J314">
+        <v>17.75391876923076</v>
       </c>
       <c r="K314">
         <v>10.93843336492891</v>
@@ -18621,10 +17995,8 @@
           <t>0.59899999999999998</t>
         </is>
       </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>11.430542769230771</t>
-        </is>
+      <c r="J315">
+        <v>11.43054276923077</v>
       </c>
       <c r="K315">
         <v>4.961504373956595</v>
@@ -18679,10 +18051,8 @@
           <t>0.49299999999999999</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>15.658566</t>
-        </is>
+      <c r="J316">
+        <v>15.658566</v>
       </c>
       <c r="K316">
         <v>8.258067261663287</v>
@@ -18737,10 +18107,8 @@
           <t>0.28399999999999997</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>12.389203384615385</t>
-        </is>
+      <c r="J317">
+        <v>12.38920338461539</v>
       </c>
       <c r="K317">
         <v>11.34222845070423</v>
@@ -18795,10 +18163,8 @@
           <t>0.27200000000000002</t>
         </is>
       </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>18.933823384615387</t>
-        </is>
+      <c r="J318">
+        <v>18.93382338461539</v>
       </c>
       <c r="K318">
         <v>18.09850764705883</v>
@@ -18853,10 +18219,8 @@
           <t>0.29899999999999999</t>
         </is>
       </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>8.2509327692307686</t>
-        </is>
+      <c r="J319">
+        <v>8.250932769230769</v>
       </c>
       <c r="K319">
         <v>7.174724147157191</v>
@@ -18911,10 +18275,8 @@
           <t>0.161</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>12.730196769230769</t>
-        </is>
+      <c r="J320">
+        <v>12.73019676923077</v>
       </c>
       <c r="K320">
         <v>20.55808173913043</v>
@@ -18969,10 +18331,8 @@
           <t>0.26400000000000001</t>
         </is>
       </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>10.985345076923075</t>
-        </is>
+      <c r="J321">
+        <v>10.98534507692307</v>
       </c>
       <c r="K321">
         <v>10.81890045454545</v>
@@ -19027,10 +18387,8 @@
           <t>0.19600000000000001</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>15.245551846153845</t>
-        </is>
+      <c r="J322">
+        <v>15.24555184615384</v>
       </c>
       <c r="K322">
         <v>20.22369122448979</v>
@@ -19085,10 +18443,8 @@
           <t>0.315</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>8.5100649230769214</t>
-        </is>
+      <c r="J323">
+        <v>8.510064923076921</v>
       </c>
       <c r="K323">
         <v>7.024180571428571</v>
@@ -19143,10 +18499,8 @@
           <t>0.255</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>9.514362461538461</t>
-        </is>
+      <c r="J324">
+        <v>9.514362461538461</v>
       </c>
       <c r="K324">
         <v>9.700918588235293</v>
@@ -19201,10 +18555,8 @@
           <t>0.186</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>13.227876923076924</t>
-        </is>
+      <c r="J325">
+        <v>13.22787692307692</v>
       </c>
       <c r="K325">
         <v>18.49058064516129</v>
@@ -19259,10 +18611,8 @@
           <t>0.184</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>11.833478769230769</t>
-        </is>
+      <c r="J326">
+        <v>11.83347876923077</v>
       </c>
       <c r="K326">
         <v>16.72122</v>
@@ -19317,10 +18667,8 @@
           <t>0.22700000000000001</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>10.777697076923078</t>
-        </is>
+      <c r="J327">
+        <v>10.77769707692308</v>
       </c>
       <c r="K327">
         <v>12.34449885462555</v>
@@ -19375,10 +18723,8 @@
           <t>0.128</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>11.953275692307693</t>
-        </is>
+      <c r="J328">
+        <v>11.95327569230769</v>
       </c>
       <c r="K328">
         <v>24.28009125</v>
@@ -19433,10 +18779,8 @@
           <t>0.23200000000000001</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>21.132049384615382</t>
-        </is>
+      <c r="J329">
+        <v>21.13204938461538</v>
       </c>
       <c r="K329">
         <v>23.68246913793103</v>
@@ -19491,10 +18835,8 @@
           <t>0.26</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>21.200457230769231</t>
-        </is>
+      <c r="J330">
+        <v>21.20045723076923</v>
       </c>
       <c r="K330">
         <v>21.20045723076923</v>
@@ -19549,10 +18891,8 @@
           <t>0.35599999999999998</t>
         </is>
       </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>21.211961538461537</t>
-        </is>
+      <c r="J331">
+        <v>21.21196153846154</v>
       </c>
       <c r="K331">
         <v>15.49188202247191</v>
@@ -19607,10 +18947,8 @@
           <t>0.17499999999999999</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>16.893425076923076</t>
-        </is>
+      <c r="J332">
+        <v>16.89342507692308</v>
       </c>
       <c r="K332">
         <v>25.09880297142858</v>
@@ -19665,10 +19003,8 @@
           <t>0.186</t>
         </is>
       </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>17.151131076923079</t>
-        </is>
+      <c r="J333">
+        <v>17.15113107692308</v>
       </c>
       <c r="K333">
         <v>23.97469935483871</v>
@@ -19723,10 +19059,8 @@
           <t>0.44400000000000001</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>8.0714750769230754</t>
-        </is>
+      <c r="J334">
+        <v>8.071475076923075</v>
       </c>
       <c r="K334">
         <v>4.726539459459459</v>
@@ -19781,10 +19115,8 @@
           <t>0.22800000000000001</t>
         </is>
       </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>17.406792923076921</t>
-        </is>
+      <c r="J335">
+        <v>17.40679292307692</v>
       </c>
       <c r="K335">
         <v>19.84985157894737</v>
@@ -19839,10 +19171,8 @@
           <t>0.219</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>16.588133076923071</t>
-        </is>
+      <c r="J336">
+        <v>16.58813307692307</v>
       </c>
       <c r="K336">
         <v>19.69367397260273</v>
@@ -19897,10 +19227,8 @@
           <t>0.13400000000000001</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>8.7873567692307688</t>
-        </is>
+      <c r="J337">
+        <v>8.787356769230769</v>
       </c>
       <c r="K337">
         <v>17.0500952238806</v>
@@ -19955,10 +19283,8 @@
           <t>0.14000000000000001</t>
         </is>
       </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>9.9866095384615381</t>
-        </is>
+      <c r="J338">
+        <v>9.986609538461538</v>
       </c>
       <c r="K338">
         <v>18.54656057142857</v>
@@ -20013,10 +19339,8 @@
           <t>0.312</t>
         </is>
       </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>15.012042923076919</t>
-        </is>
+      <c r="J339">
+        <v>15.01204292307692</v>
       </c>
       <c r="K339">
         <v>12.51003576923077</v>
@@ -20071,10 +19395,8 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>15.311820461538462</t>
-        </is>
+      <c r="J340">
+        <v>15.31182046153846</v>
       </c>
       <c r="K340">
         <v>26.5404888</v>
@@ -20129,10 +19451,8 @@
           <t>0.73</t>
         </is>
       </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>18.479355692307692</t>
-        </is>
+      <c r="J341">
+        <v>18.47935569230769</v>
       </c>
       <c r="K341">
         <v>6.581688328767124</v>
@@ -20187,10 +19507,8 @@
           <t>0.56499999999999995</t>
         </is>
       </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>17.521313076923075</t>
-        </is>
+      <c r="J342">
+        <v>17.52131307692308</v>
       </c>
       <c r="K342">
         <v>8.062905132743364</v>
@@ -20245,10 +19563,8 @@
           <t>0.59</t>
         </is>
       </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>18.855337384615385</t>
-        </is>
+      <c r="J343">
+        <v>18.85533738461539</v>
       </c>
       <c r="K343">
         <v>8.30913172881356</v>
@@ -20303,10 +19619,8 @@
           <t>0.56799999999999995</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>20.129795999999999</t>
-        </is>
+      <c r="J344">
+        <v>20.129796</v>
       </c>
       <c r="K344">
         <v>9.214343239436619</v>
@@ -20361,10 +19675,8 @@
           <t>0.55100000000000005</t>
         </is>
       </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>21.347541230769231</t>
-        </is>
+      <c r="J345">
+        <v>21.34754123076923</v>
       </c>
       <c r="K345">
         <v>10.07324994555354</v>
@@ -20419,10 +19731,8 @@
           <t>0.51900000000000002</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>17.939794153846151</t>
-        </is>
+      <c r="J346">
+        <v>17.93979415384615</v>
       </c>
       <c r="K346">
         <v>8.987180115606936</v>
@@ -20477,10 +19787,8 @@
           <t>0.58099999999999996</t>
         </is>
       </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>17.233087384615384</t>
-        </is>
+      <c r="J347">
+        <v>17.23308738461538</v>
       </c>
       <c r="K347">
         <v>7.711880757314975</v>
@@ -20535,10 +19843,8 @@
           <t>0.48499999999999999</t>
         </is>
       </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>23.895222461538459</t>
-        </is>
+      <c r="J348">
+        <v>23.89522246153846</v>
       </c>
       <c r="K348">
         <v>12.80980997938144</v>
@@ -20593,10 +19899,8 @@
           <t>0.60699999999999998</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>20.51509523076923</t>
-        </is>
+      <c r="J349">
+        <v>20.51509523076923</v>
       </c>
       <c r="K349">
         <v>8.787355453047777</v>
@@ -20651,10 +19955,8 @@
           <t>0.56200000000000006</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>20.105218615384612</t>
-        </is>
+      <c r="J350">
+        <v>20.10521861538461</v>
       </c>
       <c r="K350">
         <v>9.301346690391457</v>
@@ -20709,10 +20011,8 @@
           <t>0.88400000000000001</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>21.256457538461532</t>
-        </is>
+      <c r="J351">
+        <v>21.25645753846153</v>
       </c>
       <c r="K351">
         <v>6.251899276018098</v>
@@ -20767,10 +20067,8 @@
           <t>0.73099999999999998</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>20.882187230769233</t>
-        </is>
+      <c r="J352">
+        <v>20.88218723076923</v>
       </c>
       <c r="K352">
         <v>7.427316935704515</v>
@@ -20825,10 +20123,8 @@
           <t>0.39500000000000002</t>
         </is>
       </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>19.09150846153846</t>
-        </is>
+      <c r="J353">
+        <v>19.09150846153846</v>
       </c>
       <c r="K353">
         <v>12.56656253164557</v>
@@ -20883,10 +20179,8 @@
           <t>0.51800000000000002</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>15.885657230769228</t>
-        </is>
+      <c r="J354">
+        <v>15.88565723076923</v>
       </c>
       <c r="K354">
         <v>7.973495907335906</v>
@@ -20941,10 +20235,8 @@
           <t>0.64200000000000002</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>14.771355692307694</t>
-        </is>
+      <c r="J355">
+        <v>14.77135569230769</v>
       </c>
       <c r="K355">
         <v>5.982168971962618</v>
@@ -20999,10 +20291,8 @@
           <t>0.6</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>14.481894000000002</t>
-        </is>
+      <c r="J356">
+        <v>14.481894</v>
       </c>
       <c r="K356">
         <v>6.275487400000001</v>
@@ -21057,10 +20347,8 @@
           <t>0.54300000000000004</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>17.610352615384613</t>
-        </is>
+      <c r="J357">
+        <v>17.61035261538461</v>
       </c>
       <c r="K357">
         <v>8.432213038674032</v>
@@ -21115,10 +20403,8 @@
           <t>0.66300000000000003</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>17.366860615384613</t>
-        </is>
+      <c r="J358">
+        <v>17.36686061538461</v>
       </c>
       <c r="K358">
         <v>6.810533574660632</v>
@@ -21173,10 +20459,8 @@
           <t>0.53700000000000003</t>
         </is>
       </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>22.572322153846152</t>
-        </is>
+      <c r="J359">
+        <v>22.57232215384615</v>
       </c>
       <c r="K359">
         <v>10.92887106145251</v>
@@ -21231,10 +20515,8 @@
           <t>0.67100000000000004</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>19.246959230769232</t>
-        </is>
+      <c r="J360">
+        <v>19.24695923076923</v>
       </c>
       <c r="K360">
         <v>7.457838152011923</v>
@@ -21289,10 +20571,8 @@
           <t>0.63400000000000001</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>15.474924923076923</t>
-        </is>
+      <c r="J361">
+        <v>15.47492492307692</v>
       </c>
       <c r="K361">
         <v>6.346183722397476</v>
@@ -21347,10 +20627,8 @@
           <t>0.68</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>24.544169999999998</t>
-        </is>
+      <c r="J362">
+        <v>24.54417</v>
       </c>
       <c r="K362">
         <v>9.384535588235293</v>
@@ -21405,10 +20683,8 @@
           <t>0.68899999999999995</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>21.066731538461539</t>
-        </is>
+      <c r="J363">
+        <v>21.06673153846154</v>
       </c>
       <c r="K363">
         <v>7.949710014513789</v>
@@ -21463,10 +20739,8 @@
           <t>0.79200000000000004</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>21.06135969230769</t>
-        </is>
+      <c r="J364">
+        <v>21.06135969230769</v>
       </c>
       <c r="K364">
         <v>6.914082727272726</v>
@@ -21521,10 +20795,8 @@
           <t>0.70799999999999996</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>16.847788153846153</t>
-        </is>
+      <c r="J365">
+        <v>16.84778815384615</v>
       </c>
       <c r="K365">
         <v>6.187040847457628</v>
@@ -21579,10 +20851,8 @@
           <t>0.54</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>17.189161846153848</t>
-        </is>
+      <c r="J366">
+        <v>17.18916184615385</v>
       </c>
       <c r="K366">
         <v>8.276263111111112</v>
@@ -21637,10 +20907,8 @@
           <t>0.54200000000000004</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>25.237138153846157</t>
-        </is>
+      <c r="J367">
+        <v>25.23713815384616</v>
       </c>
       <c r="K367">
         <v>12.10637623616236</v>
@@ -21695,10 +20963,8 @@
           <t>0.28899999999999998</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>15.393539076923076</t>
-        </is>
+      <c r="J368">
+        <v>15.39353907692308</v>
       </c>
       <c r="K368">
         <v>13.84885868512111</v>
@@ -21753,10 +21019,8 @@
           <t>0.625</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>19.875084923076919</t>
-        </is>
+      <c r="J369">
+        <v>19.87508492307692</v>
       </c>
       <c r="K369">
         <v>8.268035328</v>
@@ -21811,10 +21075,8 @@
           <t>0.33900000000000002</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>26.019003230769229</t>
-        </is>
+      <c r="J370">
+        <v>26.01900323076923</v>
       </c>
       <c r="K370">
         <v>19.95557769911504</v>
@@ -21869,10 +21131,8 @@
           <t>0.73499999999999999</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>19.428128307692308</t>
-        </is>
+      <c r="J371">
+        <v>19.42812830769231</v>
       </c>
       <c r="K371">
         <v>6.872535183673469</v>
@@ -21927,10 +21187,8 @@
           <t>0.64200000000000002</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>36.755897538461539</t>
-        </is>
+      <c r="J372">
+        <v>36.75589753846154</v>
       </c>
       <c r="K372">
         <v>14.88556598130841</v>
@@ -21985,10 +21243,8 @@
           <t>0.35599999999999998</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>30.528786923076925</t>
-        </is>
+      <c r="J373">
+        <v>30.52878692307693</v>
       </c>
       <c r="K373">
         <v>22.29630505617978</v>
@@ -22043,10 +21299,8 @@
           <t>0.61799999999999999</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>15.373905692307691</t>
-        </is>
+      <c r="J374">
+        <v>15.37390569230769</v>
       </c>
       <c r="K374">
         <v>6.467986213592233</v>
@@ -22101,10 +21355,8 @@
           <t>0.42199999999999999</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>25.341817846153845</t>
-        </is>
+      <c r="J375">
+        <v>25.34181784615384</v>
       </c>
       <c r="K375">
         <v>15.61344227488152</v>
@@ -22159,10 +21411,8 @@
           <t>0.25700000000000001</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>12.531105692307694</t>
-        </is>
+      <c r="J376">
+        <v>12.53110569230769</v>
       </c>
       <c r="K376">
         <v>12.67738319066148</v>
@@ -22217,10 +21467,8 @@
           <t>0.49</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>20.689656461538462</t>
-        </is>
+      <c r="J377">
+        <v>20.68965646153846</v>
       </c>
       <c r="K377">
         <v>10.97818506122449</v>
@@ -22275,10 +21523,8 @@
           <t>0.495</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>16.640092615384614</t>
-        </is>
+      <c r="J378">
+        <v>16.64009261538461</v>
       </c>
       <c r="K378">
         <v>8.740250666666666</v>
@@ -22333,10 +21579,8 @@
           <t>0.26300000000000001</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>20.266896923076921</t>
-        </is>
+      <c r="J379">
+        <v>20.26689692307692</v>
       </c>
       <c r="K379">
         <v>20.03571558935361</v>
@@ -22391,10 +21635,8 @@
           <t>0.311</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>20.284961538461538</t>
-        </is>
+      <c r="J380">
+        <v>20.28496153846154</v>
       </c>
       <c r="K380">
         <v>16.95848874598071</v>
@@ -22449,10 +21691,8 @@
           <t>0.38100000000000001</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>17.977444615384613</t>
-        </is>
+      <c r="J381">
+        <v>17.97744461538461</v>
       </c>
       <c r="K381">
         <v>12.26807244094488</v>
@@ -22507,10 +21747,8 @@
           <t>0.26600000000000001</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>22.138058307692308</t>
-        </is>
+      <c r="J382">
+        <v>22.13805830769231</v>
       </c>
       <c r="K382">
         <v>21.63870360902256</v>
@@ -22565,10 +21803,8 @@
           <t>0.56000000000000005</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>18.233962153846154</t>
-        </is>
+      <c r="J383">
+        <v>18.23396215384615</v>
       </c>
       <c r="K383">
         <v>8.465768142857142</v>
@@ -22623,10 +21859,8 @@
           <t>0.37</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>28.61360492307692</t>
-        </is>
+      <c r="J384">
+        <v>28.61360492307692</v>
       </c>
       <c r="K384">
         <v>20.10685751351351</v>
@@ -22681,10 +21915,8 @@
           <t>0.22900000000000001</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>29.46568430769231</t>
-        </is>
+      <c r="J385">
+        <v>29.46568430769231</v>
       </c>
       <c r="K385">
         <v>33.45448873362446</v>
@@ -22739,10 +21971,8 @@
           <t>0.67400000000000004</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>26.956319076923073</t>
-        </is>
+      <c r="J386">
+        <v>26.95631907692307</v>
       </c>
       <c r="K386">
         <v>10.39858005934718</v>
@@ -22797,10 +22027,8 @@
           <t>0.23100000000000001</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>15.361545692307692</t>
-        </is>
+      <c r="J387">
+        <v>15.36154569230769</v>
       </c>
       <c r="K387">
         <v>17.29005142857143</v>
@@ -22855,10 +22083,8 @@
           <t>0.193</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>22.916975999999998</t>
-        </is>
+      <c r="J388">
+        <v>22.916976</v>
       </c>
       <c r="K388">
         <v>30.87261015544041</v>
@@ -22913,10 +22139,8 @@
           <t>0.38800000000000001</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>28.144447846153845</t>
-        </is>
+      <c r="J389">
+        <v>28.14444784615385</v>
       </c>
       <c r="K389">
         <v>18.85968154639175</v>
@@ -22971,10 +22195,8 @@
           <t>0.98</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>20.128037076923075</t>
-        </is>
+      <c r="J390">
+        <v>20.12803707692307</v>
       </c>
       <c r="K390">
         <v>5.340091469387755</v>
@@ -23029,10 +22251,8 @@
           <t>0.79700000000000004</t>
         </is>
       </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>13.559362615384615</t>
-        </is>
+      <c r="J391">
+        <v>13.55936261538461</v>
       </c>
       <c r="K391">
         <v>4.42338052697616</v>
@@ -23087,10 +22307,8 @@
           <t>0.57999999999999996</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>22.430705076923076</t>
-        </is>
+      <c r="J392">
+        <v>22.43070507692308</v>
       </c>
       <c r="K392">
         <v>10.05514365517242</v>
@@ -23145,10 +22363,8 @@
           <t>0.57999999999999996</t>
         </is>
       </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>16.231927384615386</t>
-        </is>
+      <c r="J393">
+        <v>16.23192738461539</v>
       </c>
       <c r="K393">
         <v>7.276381241379311</v>
@@ -23203,10 +22419,8 @@
           <t>0.747</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>10.297558615384617</t>
-        </is>
+      <c r="J394">
+        <v>10.29755861538462</v>
       </c>
       <c r="K394">
         <v>3.584156947791165</v>
@@ -23261,10 +22475,8 @@
           <t>0.81200000000000006</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>14.292453230769231</t>
-        </is>
+      <c r="J395">
+        <v>14.29245323076923</v>
       </c>
       <c r="K395">
         <v>4.576401280788177</v>
@@ -23319,10 +22531,8 @@
           <t>0.64500000000000002</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>21.709451538461536</t>
-        </is>
+      <c r="J396">
+        <v>21.70945153846154</v>
       </c>
       <c r="K396">
         <v>8.751096744186045</v>
@@ -23377,10 +22587,8 @@
           <t>0.60899999999999999</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>18.078416307692308</t>
-        </is>
+      <c r="J397">
+        <v>18.07841630769231</v>
       </c>
       <c r="K397">
         <v>7.718207290640395</v>
@@ -23435,10 +22643,8 @@
           <t>0.60299999999999998</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>14.988558923076925</t>
-        </is>
+      <c r="J398">
+        <v>14.98855892307692</v>
       </c>
       <c r="K398">
         <v>6.462728557213931</v>
@@ -23493,10 +22699,8 @@
           <t>0.57799999999999996</t>
         </is>
       </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>15.323514923076923</t>
-        </is>
+      <c r="J399">
+        <v>15.32351492307692</v>
       </c>
       <c r="K399">
         <v>6.892930588235295</v>
@@ -23551,10 +22755,8 @@
           <t>0.752</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr">
-        <is>
-          <t>10.510673538461539</t>
-        </is>
+      <c r="J400">
+        <v>10.51067353846154</v>
       </c>
       <c r="K400">
         <v>3.634009468085107</v>
@@ -23609,10 +22811,8 @@
           <t>0.51100000000000001</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>20.237613230769227</t>
-        </is>
+      <c r="J401">
+        <v>20.23761323076923</v>
       </c>
       <c r="K401">
         <v>10.2970243444227</v>
@@ -23667,10 +22867,8 @@
           <t>0.64600000000000002</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>18.621923538461541</t>
-        </is>
+      <c r="J402">
+        <v>18.62192353846154</v>
       </c>
       <c r="K402">
         <v>7.494891826625388</v>
@@ -23725,10 +22923,8 @@
           <t>0.61199999999999999</t>
         </is>
       </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>12.233657538461539</t>
-        </is>
+      <c r="J403">
+        <v>12.23365753846154</v>
       </c>
       <c r="K403">
         <v>5.197305490196078</v>
@@ -23783,10 +22979,8 @@
           <t>0.82499999999999996</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>15.786634615384614</t>
-        </is>
+      <c r="J404">
+        <v>15.78663461538461</v>
       </c>
       <c r="K404">
         <v>4.975181818181818</v>
@@ -23841,10 +23035,8 @@
           <t>0.75800000000000001</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr">
-        <is>
-          <t>27.113243538461539</t>
-        </is>
+      <c r="J405">
+        <v>27.11324353846154</v>
       </c>
       <c r="K405">
         <v>9.300057150395778</v>
@@ -23899,10 +23091,8 @@
           <t>0.64400000000000002</t>
         </is>
       </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>24.93640984615385</t>
-        </is>
+      <c r="J406">
+        <v>24.93640984615385</v>
       </c>
       <c r="K406">
         <v>10.06749465838509</v>
@@ -23957,10 +23147,8 @@
           <t>0.72599999999999998</t>
         </is>
       </c>
-      <c r="J407" t="inlineStr">
-        <is>
-          <t>13.422356769230769</t>
-        </is>
+      <c r="J407">
+        <v>13.42235676923077</v>
       </c>
       <c r="K407">
         <v>4.806904628099174</v>
@@ -24015,10 +23203,8 @@
           <t>0.81599999999999995</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>19.593894923076924</t>
-        </is>
+      <c r="J408">
+        <v>19.59389492307692</v>
       </c>
       <c r="K408">
         <v>6.243152794117648</v>
@@ -24073,10 +23259,8 @@
           <t>0.754</t>
         </is>
       </c>
-      <c r="J409" t="inlineStr">
-        <is>
-          <t>21.012632769230766</t>
-        </is>
+      <c r="J409">
+        <v>21.01263276923077</v>
       </c>
       <c r="K409">
         <v>7.245735437665782</v>
@@ -24131,10 +23315,8 @@
           <t>0.65400000000000003</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>18.800240307692309</t>
-        </is>
+      <c r="J410">
+        <v>18.80024030769231</v>
       </c>
       <c r="K410">
         <v>7.474101651376147</v>
@@ -24189,10 +23371,8 @@
           <t>0.82599999999999996</t>
         </is>
       </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>15.548704615384613</t>
-        </is>
+      <c r="J411">
+        <v>15.54870461538461</v>
       </c>
       <c r="K411">
         <v>4.894265375302663</v>
@@ -24247,10 +23427,8 @@
           <t>0.66600000000000004</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>18.857619230769231</t>
-        </is>
+      <c r="J412">
+        <v>18.85761923076923</v>
       </c>
       <c r="K412">
         <v>7.361833333333333</v>
@@ -24305,10 +23483,8 @@
           <t>0.64700000000000002</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>25.565581384615388</t>
-        </is>
+      <c r="J413">
+        <v>25.56558138461539</v>
       </c>
       <c r="K413">
         <v>10.27364939721793</v>
@@ -24363,10 +23539,8 @@
           <t>0.84799999999999998</t>
         </is>
       </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>20.708624307692304</t>
-        </is>
+      <c r="J414">
+        <v>20.7086243076923</v>
       </c>
       <c r="K414">
         <v>6.349342358490565</v>
@@ -24421,10 +23595,8 @@
           <t>0.80800000000000005</t>
         </is>
       </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>18.288203538461538</t>
-        </is>
+      <c r="J415">
+        <v>18.28820353846154</v>
       </c>
       <c r="K415">
         <v>5.884817970297029</v>
@@ -24479,10 +23651,8 @@
           <t>0.68799999999999994</t>
         </is>
       </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>20.807409230769228</t>
-        </is>
+      <c r="J416">
+        <v>20.80740923076923</v>
       </c>
       <c r="K416">
         <v>7.86326511627907</v>
@@ -24537,10 +23707,8 @@
           <t>0.64900000000000002</t>
         </is>
       </c>
-      <c r="J417" t="inlineStr">
-        <is>
-          <t>24.585433384615385</t>
-        </is>
+      <c r="J417">
+        <v>24.58543338461538</v>
       </c>
       <c r="K417">
         <v>9.849326163328197</v>
@@ -24595,10 +23763,8 @@
           <t>0.68200000000000005</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>22.422148153846152</t>
-        </is>
+      <c r="J418">
+        <v>22.42214815384615</v>
       </c>
       <c r="K418">
         <v>8.548033020527859</v>
@@ -24653,10 +23819,8 @@
           <t>0.66900000000000004</t>
         </is>
       </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>26.245476461538459</t>
-        </is>
+      <c r="J419">
+        <v>26.24547646153846</v>
       </c>
       <c r="K419">
         <v>10.20003569506726</v>
@@ -24711,10 +23875,8 @@
           <t>0.10100000000000001</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>16.661199692307694</t>
-        </is>
+      <c r="J420">
+        <v>16.66119969230769</v>
       </c>
       <c r="K420">
         <v>42.89021702970297</v>
@@ -24769,10 +23931,8 @@
           <t>0.20300000000000001</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>16.12173323076923</t>
-        </is>
+      <c r="J421">
+        <v>16.12173323076923</v>
       </c>
       <c r="K421">
         <v>20.64852532019704</v>
@@ -24827,10 +23987,8 @@
           <t>9.7000000000000003E-2</t>
         </is>
       </c>
-      <c r="J422" t="inlineStr">
-        <is>
-          <t>14.860014923076923</t>
-        </is>
+      <c r="J422">
+        <v>14.86001492307692</v>
       </c>
       <c r="K422">
         <v>39.83096783505155</v>
@@ -24885,10 +24043,8 @@
           <t>0.16400000000000001</t>
         </is>
       </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>15.171914769230769</t>
-        </is>
+      <c r="J423">
+        <v>15.17191476923077</v>
       </c>
       <c r="K423">
         <v>24.0530356097561</v>
@@ -24943,10 +24099,8 @@
           <t>0.16700000000000001</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>18.353283692307691</t>
-        </is>
+      <c r="J424">
+        <v>18.35328369230769</v>
       </c>
       <c r="K424">
         <v>28.57397461077844</v>
@@ -25001,10 +24155,8 @@
           <t>9.8000000000000004E-2</t>
         </is>
       </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>18.328325999999993</t>
-        </is>
+      <c r="J425">
+        <v>18.32832599999999</v>
       </c>
       <c r="K425">
         <v>48.62617102040815</v>
@@ -25059,10 +24211,8 @@
           <t>0.122</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>17.270642769230768</t>
-        </is>
+      <c r="J426">
+        <v>17.27064276923077</v>
       </c>
       <c r="K426">
         <v>36.80628786885246</v>
@@ -25117,10 +24267,8 @@
           <t>9.4E-2</t>
         </is>
       </c>
-      <c r="J427" t="inlineStr">
-        <is>
-          <t>15.959627076923075</t>
-        </is>
+      <c r="J427">
+        <v>15.95962707692308</v>
       </c>
       <c r="K427">
         <v>44.14364936170212</v>
@@ -25175,10 +24323,8 @@
           <t>0.27800000000000002</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>14.163053538461538</t>
-        </is>
+      <c r="J428">
+        <v>14.16305353846154</v>
       </c>
       <c r="K428">
         <v>13.24602129496403</v>
@@ -25233,10 +24379,8 @@
           <t>0.23300000000000001</t>
         </is>
       </c>
-      <c r="J429" t="inlineStr">
-        <is>
-          <t>11.237774307692307</t>
-        </is>
+      <c r="J429">
+        <v>11.23777430769231</v>
       </c>
       <c r="K429">
         <v>12.54000566523605</v>
@@ -25291,10 +24435,8 @@
           <t>0.28899999999999998</t>
         </is>
       </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>14.20892815384615</t>
-        </is>
+      <c r="J430">
+        <v>14.20892815384615</v>
       </c>
       <c r="K430">
         <v>12.78311875432526</v>
@@ -25349,10 +24491,8 @@
           <t>0.34300000000000003</t>
         </is>
       </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>11.448179538461538</t>
-        </is>
+      <c r="J431">
+        <v>11.44817953846154</v>
       </c>
       <c r="K431">
         <v>8.677920349854228</v>
@@ -25407,10 +24547,8 @@
           <t>0.27500000000000002</t>
         </is>
       </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>13.269140307692304</t>
-        </is>
+      <c r="J432">
+        <v>13.2691403076923</v>
       </c>
       <c r="K432">
         <v>12.54536901818181</v>
@@ -25465,10 +24603,8 @@
           <t>0.34399999999999997</t>
         </is>
       </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>9.2084049230769214</t>
-        </is>
+      <c r="J433">
+        <v>9.208404923076921</v>
       </c>
       <c r="K433">
         <v>6.959840930232558</v>
@@ -25523,10 +24659,8 @@
           <t>0.29699999999999999</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>10.624147846153845</t>
-        </is>
+      <c r="J434">
+        <v>10.62414784615384</v>
       </c>
       <c r="K434">
         <v>9.300600808080807</v>
@@ -25581,10 +24715,8 @@
           <t>0.23200000000000001</t>
         </is>
       </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>19.510987846153846</t>
-        </is>
+      <c r="J435">
+        <v>19.51098784615385</v>
       </c>
       <c r="K435">
         <v>21.86576224137931</v>
@@ -25639,10 +24771,8 @@
           <t>0.32700000000000001</t>
         </is>
       </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>8.9656260000000021</t>
-        </is>
+      <c r="J436">
+        <v>8.965626000000002</v>
       </c>
       <c r="K436">
         <v>7.128632293577983</v>
@@ -25697,10 +24827,8 @@
           <t>0.32900000000000001</t>
         </is>
       </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>11.526095076923076</t>
-        </is>
+      <c r="J437">
+        <v>11.52609507692308</v>
       </c>
       <c r="K437">
         <v>9.108768145896656</v>
@@ -25755,10 +24883,8 @@
           <t>0.26900000000000002</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>10.124518615384616</t>
-        </is>
+      <c r="J438">
+        <v>10.12451861538462</v>
       </c>
       <c r="K438">
         <v>9.785780074349443</v>
@@ -25813,10 +24939,8 @@
           <t>0.33700000000000002</t>
         </is>
       </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>8.3112115384615386</t>
-        </is>
+      <c r="J439">
+        <v>8.311211538461539</v>
       </c>
       <c r="K439">
         <v>6.412210682492582</v>
@@ -25871,10 +24995,8 @@
           <t>0.29599999999999999</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>12.031048615384613</t>
-        </is>
+      <c r="J440">
+        <v>12.03104861538461</v>
       </c>
       <c r="K440">
         <v>10.56781297297297</v>
@@ -25929,10 +25051,8 @@
           <t>0.32300000000000001</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>13.045614461538461</t>
-        </is>
+      <c r="J441">
+        <v>13.04561446153846</v>
       </c>
       <c r="K441">
         <v>10.50111380804953</v>
@@ -25987,10 +25107,8 @@
           <t>0.23599999999999999</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>8.2367663076923066</t>
-        </is>
+      <c r="J442">
+        <v>8.236766307692307</v>
       </c>
       <c r="K442">
         <v>9.074403559322034</v>
@@ -26045,10 +25163,8 @@
           <t>0.378</t>
         </is>
       </c>
-      <c r="J443" t="inlineStr">
-        <is>
-          <t>11.556377076923075</t>
-        </is>
+      <c r="J443">
+        <v>11.55637707692308</v>
       </c>
       <c r="K443">
         <v>7.948830793650793</v>
@@ -26103,10 +25219,8 @@
           <t>0.314</t>
         </is>
       </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>15.311677846153845</t>
-        </is>
+      <c r="J444">
+        <v>15.31167784615385</v>
       </c>
       <c r="K444">
         <v>12.67845936305732</v>
@@ -26161,10 +25275,8 @@
           <t>0.33800000000000002</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>16.350773538461539</t>
-        </is>
+      <c r="J445">
+        <v>16.35077353846154</v>
       </c>
       <c r="K445">
         <v>12.57751810650888</v>
@@ -26219,10 +25331,8 @@
           <t>0.23</t>
         </is>
       </c>
-      <c r="J446" t="inlineStr">
-        <is>
-          <t>11.05227923076923</t>
-        </is>
+      <c r="J446">
+        <v>11.05227923076923</v>
       </c>
       <c r="K446">
         <v>12.49388086956522</v>
@@ -26277,10 +25387,8 @@
           <t>0.20899999999999999</t>
         </is>
       </c>
-      <c r="J447" t="inlineStr">
-        <is>
-          <t>13.799051538461537</t>
-        </is>
+      <c r="J447">
+        <v>13.79905153846154</v>
       </c>
       <c r="K447">
         <v>17.16628421052631</v>
@@ -26335,10 +25443,8 @@
           <t>0.27100000000000002</t>
         </is>
       </c>
-      <c r="J448" t="inlineStr">
-        <is>
-          <t>11.748670153846154</t>
-        </is>
+      <c r="J448">
+        <v>11.74867015384615</v>
       </c>
       <c r="K448">
         <v>11.27178686346863</v>
@@ -26393,10 +25499,8 @@
           <t>0.36699999999999999</t>
         </is>
       </c>
-      <c r="J449" t="inlineStr">
-        <is>
-          <t>17.461271999999997</t>
-        </is>
+      <c r="J449">
+        <v>17.461272</v>
       </c>
       <c r="K449">
         <v>12.37038343324251</v>
@@ -26451,10 +25555,8 @@
           <t>0.38900000000000001</t>
         </is>
       </c>
-      <c r="J450" t="inlineStr">
-        <is>
-          <t>13.582703999999998</t>
-        </is>
+      <c r="J450">
+        <v>13.582704</v>
       </c>
       <c r="K450">
         <v>9.078413984575834</v>
@@ -26509,10 +25611,8 @@
           <t>0.26600000000000001</t>
         </is>
       </c>
-      <c r="J451" t="inlineStr">
-        <is>
-          <t>13.74671169230769</t>
-        </is>
+      <c r="J451">
+        <v>13.74671169230769</v>
       </c>
       <c r="K451">
         <v>13.4366354887218</v>
@@ -26567,10 +25667,8 @@
           <t>0.29199999999999998</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr">
-        <is>
-          <t>14.440583076923076</t>
-        </is>
+      <c r="J452">
+        <v>14.44058307692308</v>
       </c>
       <c r="K452">
         <v>12.85805342465754</v>
@@ -26625,10 +25723,8 @@
           <t>0.38400000000000001</t>
         </is>
       </c>
-      <c r="J453" t="inlineStr">
-        <is>
-          <t>14.723627076923076</t>
-        </is>
+      <c r="J453">
+        <v>14.72362707692308</v>
       </c>
       <c r="K453">
         <v>9.969122499999999</v>
@@ -26683,10 +25779,8 @@
           <t>0.30299999999999999</t>
         </is>
       </c>
-      <c r="J454" t="inlineStr">
-        <is>
-          <t>10.191024923076922</t>
-        </is>
+      <c r="J454">
+        <v>10.19102492307692</v>
       </c>
       <c r="K454">
         <v>8.74477386138614</v>
@@ -26741,10 +25835,8 @@
           <t>0.34100000000000003</t>
         </is>
       </c>
-      <c r="J455" t="inlineStr">
-        <is>
-          <t>16.237061538461539</t>
-        </is>
+      <c r="J455">
+        <v>16.23706153846154</v>
       </c>
       <c r="K455">
         <v>12.3801642228739</v>
@@ -26799,10 +25891,8 @@
           <t>0.35299999999999998</t>
         </is>
       </c>
-      <c r="J456" t="inlineStr">
-        <is>
-          <t>15.32817369230769</t>
-        </is>
+      <c r="J456">
+        <v>15.32817369230769</v>
       </c>
       <c r="K456">
         <v>11.28987297450425</v>
@@ -26857,10 +25947,8 @@
           <t>0.27400000000000002</t>
         </is>
       </c>
-      <c r="J457" t="inlineStr">
-        <is>
-          <t>10.522938461538459</t>
-        </is>
+      <c r="J457">
+        <v>10.52293846153846</v>
       </c>
       <c r="K457">
         <v>9.985270072992698</v>
@@ -26915,10 +26003,8 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>12.888737538461536</t>
-        </is>
+      <c r="J458">
+        <v>12.88873753846154</v>
       </c>
       <c r="K458">
         <v>11.1702392</v>
@@ -26973,10 +26059,8 @@
           <t>0.307</t>
         </is>
       </c>
-      <c r="J459" t="inlineStr">
-        <is>
-          <t>13.258396615384616</t>
-        </is>
+      <c r="J459">
+        <v>13.25839661538462</v>
       </c>
       <c r="K459">
         <v>11.22860951140065</v>
@@ -27031,10 +26115,8 @@
           <t>0.24299999999999999</t>
         </is>
       </c>
-      <c r="J460" t="inlineStr">
-        <is>
-          <t>11.846076461538461</t>
-        </is>
+      <c r="J460">
+        <v>11.84607646153846</v>
       </c>
       <c r="K460">
         <v>12.67481432098765</v>
@@ -27089,10 +26171,8 @@
           <t>0.23899999999999999</t>
         </is>
       </c>
-      <c r="J461" t="inlineStr">
-        <is>
-          <t>6.2864058461538459</t>
-        </is>
+      <c r="J461">
+        <v>6.286405846153846</v>
       </c>
       <c r="K461">
         <v>6.838767866108787</v>
@@ -27147,10 +26227,8 @@
           <t>0.245</t>
         </is>
       </c>
-      <c r="J462" t="inlineStr">
-        <is>
-          <t>14.762703692307692</t>
-        </is>
+      <c r="J462">
+        <v>14.76270369230769</v>
       </c>
       <c r="K462">
         <v>15.66654269387755</v>
@@ -27205,10 +26283,8 @@
           <t>0.26200000000000001</t>
         </is>
       </c>
-      <c r="J463" t="inlineStr">
-        <is>
-          <t>16.272620307692303</t>
-        </is>
+      <c r="J463">
+        <v>16.2726203076923</v>
       </c>
       <c r="K463">
         <v>16.14840183206107</v>
@@ -27263,10 +26339,8 @@
           <t>0.47899999999999998</t>
         </is>
       </c>
-      <c r="J464" t="inlineStr">
-        <is>
-          <t>13.710772615384615</t>
-        </is>
+      <c r="J464">
+        <v>13.71077261538461</v>
       </c>
       <c r="K464">
         <v>7.442173027139875</v>
@@ -27321,10 +26395,8 @@
           <t>0.47799999999999998</t>
         </is>
       </c>
-      <c r="J465" t="inlineStr">
-        <is>
-          <t>16.077379846153846</t>
-        </is>
+      <c r="J465">
+        <v>16.07737984615385</v>
       </c>
       <c r="K465">
         <v>8.745018326359833</v>
@@ -27379,10 +26451,8 @@
           <t>0.38400000000000001</t>
         </is>
       </c>
-      <c r="J466" t="inlineStr">
-        <is>
-          <t>16.47622753846154</t>
-        </is>
+      <c r="J466">
+        <v>16.47622753846154</v>
       </c>
       <c r="K466">
         <v>11.1557790625</v>
@@ -27437,10 +26507,8 @@
           <t>0.28299999999999997</t>
         </is>
       </c>
-      <c r="J467" t="inlineStr">
-        <is>
-          <t>14.039358461538461</t>
-        </is>
+      <c r="J467">
+        <v>14.03935846153846</v>
       </c>
       <c r="K467">
         <v>12.89835053003534</v>
@@ -27495,10 +26563,8 @@
           <t>0.26600000000000001</t>
         </is>
       </c>
-      <c r="J468" t="inlineStr">
-        <is>
-          <t>12.905994</t>
-        </is>
+      <c r="J468">
+        <v>12.905994</v>
       </c>
       <c r="K468">
         <v>12.61488135338346</v>
@@ -27553,10 +26619,8 @@
           <t>0.22600000000000001</t>
         </is>
       </c>
-      <c r="J469" t="inlineStr">
-        <is>
-          <t>13.245133384615386</t>
-        </is>
+      <c r="J469">
+        <v>13.24513338461539</v>
       </c>
       <c r="K469">
         <v>15.23776407079646</v>
@@ -27611,10 +26675,8 @@
           <t>0.26300000000000001</t>
         </is>
       </c>
-      <c r="J470" t="inlineStr">
-        <is>
-          <t>7.5392344615384612</t>
-        </is>
+      <c r="J470">
+        <v>7.539234461538461</v>
       </c>
       <c r="K470">
         <v>7.453235589353612</v>
@@ -27669,10 +26731,8 @@
           <t>0.315</t>
         </is>
       </c>
-      <c r="J471" t="inlineStr">
-        <is>
-          <t>16.182534923076926</t>
-        </is>
+      <c r="J471">
+        <v>16.18253492307693</v>
       </c>
       <c r="K471">
         <v>13.35701295238095</v>
@@ -27727,10 +26787,8 @@
           <t>0.249</t>
         </is>
       </c>
-      <c r="J472" t="inlineStr">
-        <is>
-          <t>13.35865523076923</t>
-        </is>
+      <c r="J472">
+        <v>13.35865523076923</v>
       </c>
       <c r="K472">
         <v>13.94879662650602</v>
@@ -27785,10 +26843,8 @@
           <t>0.33200000000000002</t>
         </is>
       </c>
-      <c r="J473" t="inlineStr">
-        <is>
-          <t>13.760688</t>
-        </is>
+      <c r="J473">
+        <v>13.760688</v>
       </c>
       <c r="K473">
         <v>10.77644240963856</v>
@@ -27843,10 +26899,8 @@
           <t>0.22600000000000001</t>
         </is>
       </c>
-      <c r="J474" t="inlineStr">
-        <is>
-          <t>13.384611230769229</t>
-        </is>
+      <c r="J474">
+        <v>13.38461123076923</v>
       </c>
       <c r="K474">
         <v>15.39822530973451</v>
@@ -27901,10 +26955,8 @@
           <t>0.314</t>
         </is>
       </c>
-      <c r="J475" t="inlineStr">
-        <is>
-          <t>12.426948923076923</t>
-        </is>
+      <c r="J475">
+        <v>12.42694892307692</v>
       </c>
       <c r="K475">
         <v>10.28983031847134</v>
@@ -27959,10 +27011,8 @@
           <t>0.53600000000000003</t>
         </is>
       </c>
-      <c r="J476" t="inlineStr">
-        <is>
-          <t>20.320710461538464</t>
-        </is>
+      <c r="J476">
+        <v>20.32071046153846</v>
       </c>
       <c r="K476">
         <v>9.85706104477612</v>
@@ -28017,10 +27067,8 @@
           <t>0.30199999999999999</t>
         </is>
       </c>
-      <c r="J477" t="inlineStr">
-        <is>
-          <t>15.11344246153846</t>
-        </is>
+      <c r="J477">
+        <v>15.11344246153846</v>
       </c>
       <c r="K477">
         <v>13.01157298013245</v>
@@ -28075,10 +27123,8 @@
           <t>0.20599999999999999</t>
         </is>
       </c>
-      <c r="J478" t="inlineStr">
-        <is>
-          <t>11.219947384615384</t>
-        </is>
+      <c r="J478">
+        <v>11.21994738461538</v>
       </c>
       <c r="K478">
         <v>14.1610986407767</v>
@@ -28133,10 +27179,8 @@
           <t>0.22700000000000001</t>
         </is>
       </c>
-      <c r="J479" t="inlineStr">
-        <is>
-          <t>9.6922989230769208</t>
-        </is>
+      <c r="J479">
+        <v>9.692298923076921</v>
       </c>
       <c r="K479">
         <v>11.10131154185022</v>
@@ -28191,10 +27235,8 @@
           <t>0.40200000000000002</t>
         </is>
       </c>
-      <c r="J480" t="inlineStr">
-        <is>
-          <t>16.177495846153846</t>
-        </is>
+      <c r="J480">
+        <v>16.17749584615385</v>
       </c>
       <c r="K480">
         <v>10.46305701492537</v>
@@ -28249,10 +27291,8 @@
           <t>0.316</t>
         </is>
       </c>
-      <c r="J481" t="inlineStr">
-        <is>
-          <t>17.019497076923077</t>
-        </is>
+      <c r="J481">
+        <v>17.01949707692308</v>
       </c>
       <c r="K481">
         <v>14.00338367088608</v>
@@ -28307,10 +27347,8 @@
           <t>0.193</t>
         </is>
       </c>
-      <c r="J482" t="inlineStr">
-        <is>
-          <t>10.285293692307693</t>
-        </is>
+      <c r="J482">
+        <v>10.28529369230769</v>
       </c>
       <c r="K482">
         <v>13.85583606217617</v>
@@ -28365,10 +27403,8 @@
           <t>0.18099999999999999</t>
         </is>
       </c>
-      <c r="J483" t="inlineStr">
-        <is>
-          <t>14.318409230769232</t>
-        </is>
+      <c r="J483">
+        <v>14.31840923076923</v>
       </c>
       <c r="K483">
         <v>20.56788066298343</v>
@@ -28423,10 +27459,8 @@
           <t>0.28000000000000003</t>
         </is>
       </c>
-      <c r="J484" t="inlineStr">
-        <is>
-          <t>14.347550307692307</t>
-        </is>
+      <c r="J484">
+        <v>14.34755030769231</v>
       </c>
       <c r="K484">
         <v>13.32272528571428</v>
@@ -28481,10 +27515,8 @@
           <t>0.28499999999999998</t>
         </is>
       </c>
-      <c r="J485" t="inlineStr">
-        <is>
-          <t>10.080640615384615</t>
-        </is>
+      <c r="J485">
+        <v>10.08064061538462</v>
       </c>
       <c r="K485">
         <v>9.196373894736842</v>
@@ -28539,10 +27571,8 @@
           <t>0.307</t>
         </is>
       </c>
-      <c r="J486" t="inlineStr">
-        <is>
-          <t>15.242747076923077</t>
-        </is>
+      <c r="J486">
+        <v>15.24274707692308</v>
       </c>
       <c r="K486">
         <v>12.90916690553746</v>
@@ -28597,10 +27627,8 @@
           <t>0.35099999999999998</t>
         </is>
       </c>
-      <c r="J487" t="inlineStr">
-        <is>
-          <t>14.513412000000001</t>
-        </is>
+      <c r="J487">
+        <v>14.513412</v>
       </c>
       <c r="K487">
         <v>10.75067555555556</v>
@@ -28655,10 +27683,8 @@
           <t>0.58699999999999997</t>
         </is>
       </c>
-      <c r="J488" t="inlineStr">
-        <is>
-          <t>25.422395538461533</t>
-        </is>
+      <c r="J488">
+        <v>25.42239553846153</v>
       </c>
       <c r="K488">
         <v>11.26034555366269</v>
@@ -28713,10 +27739,8 @@
           <t>0.95799999999999996</t>
         </is>
       </c>
-      <c r="J489" t="inlineStr">
-        <is>
-          <t>26.744202461538457</t>
-        </is>
+      <c r="J489">
+        <v>26.74420246153846</v>
       </c>
       <c r="K489">
         <v>7.258343048016701</v>
@@ -28771,10 +27795,8 @@
           <t>0.77600000000000002</t>
         </is>
       </c>
-      <c r="J490" t="inlineStr">
-        <is>
-          <t>22.39329230769231</t>
-        </is>
+      <c r="J490">
+        <v>22.39329230769231</v>
       </c>
       <c r="K490">
         <v>7.502907216494846</v>
@@ -28829,10 +27851,8 @@
           <t>0.45500000000000002</t>
         </is>
       </c>
-      <c r="J491" t="inlineStr">
-        <is>
-          <t>16.205781230769233</t>
-        </is>
+      <c r="J491">
+        <v>16.20578123076923</v>
       </c>
       <c r="K491">
         <v>9.260446417582418</v>
@@ -28887,10 +27907,8 @@
           <t>0.69699999999999995</t>
         </is>
       </c>
-      <c r="J492" t="inlineStr">
-        <is>
-          <t>18.486486461538462</t>
-        </is>
+      <c r="J492">
+        <v>18.48648646153846</v>
       </c>
       <c r="K492">
         <v>6.895963385939742</v>
@@ -28945,10 +27963,8 @@
           <t>0.56100000000000005</t>
         </is>
       </c>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>10.987008923076923</t>
-        </is>
+      <c r="J493">
+        <v>10.98700892307692</v>
       </c>
       <c r="K493">
         <v>5.092018395721925</v>
@@ -29003,10 +28019,8 @@
           <t>0.69299999999999995</t>
         </is>
       </c>
-      <c r="J494" t="inlineStr">
-        <is>
-          <t>16.760460000000002</t>
-        </is>
+      <c r="J494">
+        <v>16.76046</v>
       </c>
       <c r="K494">
         <v>6.288195670995671</v>
@@ -29061,10 +28075,8 @@
           <t>0.85099999999999998</t>
         </is>
       </c>
-      <c r="J495" t="inlineStr">
-        <is>
-          <t>29.291931230769233</t>
-        </is>
+      <c r="J495">
+        <v>29.29193123076923</v>
       </c>
       <c r="K495">
         <v>8.949356192714456</v>
@@ -29119,10 +28131,8 @@
           <t>0.91400000000000003</t>
         </is>
       </c>
-      <c r="J496" t="inlineStr">
-        <is>
-          <t>20.130889384615383</t>
-        </is>
+      <c r="J496">
+        <v>20.13088938461538</v>
       </c>
       <c r="K496">
         <v>5.726511203501094</v>
@@ -29177,10 +28187,8 @@
           <t>0.191</t>
         </is>
       </c>
-      <c r="J497" t="inlineStr">
-        <is>
-          <t>12.157168153846154</t>
-        </is>
+      <c r="J497">
+        <v>12.15716815384615</v>
       </c>
       <c r="K497">
         <v>16.54902471204188</v>
@@ -29235,10 +28243,8 @@
           <t>0.51100000000000001</t>
         </is>
       </c>
-      <c r="J498" t="inlineStr">
-        <is>
-          <t>17.157548769230768</t>
-        </is>
+      <c r="J498">
+        <v>17.15754876923077</v>
       </c>
       <c r="K498">
         <v>8.729868258317024</v>
@@ -29293,10 +28299,8 @@
           <t>0.67</t>
         </is>
       </c>
-      <c r="J499" t="inlineStr">
-        <is>
-          <t>12.948445846153845</t>
-        </is>
+      <c r="J499">
+        <v>12.94844584615385</v>
       </c>
       <c r="K499">
         <v>5.024770029850746</v>
@@ -29351,10 +28355,8 @@
           <t>0.628</t>
         </is>
       </c>
-      <c r="J500" t="inlineStr">
-        <is>
-          <t>15.314292461538459</t>
-        </is>
+      <c r="J500">
+        <v>15.31429246153846</v>
       </c>
       <c r="K500">
         <v>6.340312165605094</v>
@@ -29409,10 +28411,8 @@
           <t>0.436</t>
         </is>
       </c>
-      <c r="J501" t="inlineStr">
-        <is>
-          <t>17.784676153846156</t>
-        </is>
+      <c r="J501">
+        <v>17.78467615384616</v>
       </c>
       <c r="K501">
         <v>10.60554082568807</v>
@@ -29467,10 +28467,8 @@
           <t>0.70099999999999996</t>
         </is>
       </c>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>16.657634307692305</t>
-        </is>
+      <c r="J502">
+        <v>16.65763430769231</v>
       </c>
       <c r="K502">
         <v>6.178295178316691</v>
@@ -29525,10 +28523,8 @@
           <t>0.70399999999999996</t>
         </is>
       </c>
-      <c r="J503" t="inlineStr">
-        <is>
-          <t>29.291313230769227</t>
-        </is>
+      <c r="J503">
+        <v>29.29131323076923</v>
       </c>
       <c r="K503">
         <v>10.81781454545454</v>
@@ -29583,10 +28579,8 @@
           <t>0.44700000000000001</t>
         </is>
       </c>
-      <c r="J504" t="inlineStr">
-        <is>
-          <t>24.860728615384613</t>
-        </is>
+      <c r="J504">
+        <v>24.86072861538461</v>
       </c>
       <c r="K504">
         <v>14.46037906040268</v>
@@ -29641,10 +28635,8 @@
           <t>0.67100000000000004</t>
         </is>
       </c>
-      <c r="J505" t="inlineStr">
-        <is>
-          <t>18.706969846153847</t>
-        </is>
+      <c r="J505">
+        <v>18.70696984615385</v>
       </c>
       <c r="K505">
         <v>7.248602324888227</v>
@@ -29699,10 +28691,8 @@
           <t>0.29299999999999998</t>
         </is>
       </c>
-      <c r="J506" t="inlineStr">
-        <is>
-          <t>14.887064307692309</t>
-        </is>
+      <c r="J506">
+        <v>14.88706430769231</v>
       </c>
       <c r="K506">
         <v>13.21036423208191</v>
@@ -29757,10 +28747,8 @@
           <t>0.629</t>
         </is>
       </c>
-      <c r="J507" t="inlineStr">
-        <is>
-          <t>20.019364153846155</t>
-        </is>
+      <c r="J507">
+        <v>20.01936415384615</v>
       </c>
       <c r="K507">
         <v>8.275094880763117</v>
@@ -29815,10 +28803,8 @@
           <t>0.55500000000000005</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>8.7454278461538451</t>
-        </is>
+      <c r="J508">
+        <v>8.745427846153845</v>
       </c>
       <c r="K508">
         <v>4.096957189189188</v>
@@ -29873,10 +28859,8 @@
           <t>0.60399999999999998</t>
         </is>
       </c>
-      <c r="J509" t="inlineStr">
-        <is>
-          <t>12.32283969230769</t>
-        </is>
+      <c r="J509">
+        <v>12.32283969230769</v>
       </c>
       <c r="K509">
         <v>5.304533642384106</v>
@@ -29931,10 +28915,8 @@
           <t>0.66700000000000004</t>
         </is>
       </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>18.990917076923076</t>
-        </is>
+      <c r="J510">
+        <v>18.99091707692308</v>
       </c>
       <c r="K510">
         <v>7.40275628185907</v>
@@ -29989,10 +28971,8 @@
           <t>0.71399999999999997</t>
         </is>
       </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>19.53494723076923</t>
-        </is>
+      <c r="J511">
+        <v>19.53494723076923</v>
       </c>
       <c r="K511">
         <v>7.113566218487396</v>
@@ -30047,10 +29027,8 @@
           <t>0.997</t>
         </is>
       </c>
-      <c r="J512" t="inlineStr">
-        <is>
-          <t>16.612377692307692</t>
-        </is>
+      <c r="J512">
+        <v>16.61237769230769</v>
       </c>
       <c r="K512">
         <v>4.332214844533601</v>
@@ -30105,10 +29083,8 @@
           <t>0.51</t>
         </is>
       </c>
-      <c r="J513" t="inlineStr">
-        <is>
-          <t>18.476265692307692</t>
-        </is>
+      <c r="J513">
+        <v>18.47626569230769</v>
       </c>
       <c r="K513">
         <v>9.419272705882353</v>
@@ -30163,10 +29139,8 @@
           <t>0.66800000000000004</t>
         </is>
       </c>
-      <c r="J514" t="inlineStr">
-        <is>
-          <t>23.381474307692304</t>
-        </is>
+      <c r="J514">
+        <v>23.3814743076923</v>
       </c>
       <c r="K514">
         <v>9.100573832335328</v>
@@ -30221,10 +29195,8 @@
           <t>0.59199999999999997</t>
         </is>
       </c>
-      <c r="J515" t="inlineStr">
-        <is>
-          <t>18.426445384615384</t>
-        </is>
+      <c r="J515">
+        <v>18.42644538461538</v>
       </c>
       <c r="K515">
         <v>8.092695608108109</v>
@@ -30279,10 +29251,8 @@
           <t>0.90400000000000003</t>
         </is>
       </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t>16.225319538461537</t>
-        </is>
+      <c r="J516">
+        <v>16.22531953846154</v>
       </c>
       <c r="K516">
         <v>4.666574203539823</v>
@@ -30337,10 +29307,8 @@
           <t>0.68400000000000005</t>
         </is>
       </c>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t>9.3737912307692319</t>
-        </is>
+      <c r="J517">
+        <v>9.373791230769232</v>
       </c>
       <c r="K517">
         <v>3.56313701754386</v>
@@ -30395,10 +29363,8 @@
           <t>0.73199999999999998</t>
         </is>
       </c>
-      <c r="J518" t="inlineStr">
-        <is>
-          <t>12.052203230769232</t>
-        </is>
+      <c r="J518">
+        <v>12.05220323076923</v>
       </c>
       <c r="K518">
         <v>4.280837213114754</v>
@@ -30453,10 +29419,8 @@
           <t>0.73499999999999999</t>
         </is>
       </c>
-      <c r="J519" t="inlineStr">
-        <is>
-          <t>10.491325384615383</t>
-        </is>
+      <c r="J519">
+        <v>10.49132538461538</v>
       </c>
       <c r="K519">
         <v>3.711217142857143</v>
@@ -30511,10 +29475,8 @@
           <t>0.66600000000000004</t>
         </is>
       </c>
-      <c r="J520" t="inlineStr">
-        <is>
-          <t>11.176116923076922</t>
-        </is>
+      <c r="J520">
+        <v>11.17611692307692</v>
       </c>
       <c r="K520">
         <v>4.363048648648649</v>
@@ -30569,10 +29531,8 @@
           <t>0.75900000000000001</t>
         </is>
       </c>
-      <c r="J521" t="inlineStr">
-        <is>
-          <t>11.686014461538463</t>
-        </is>
+      <c r="J521">
+        <v>11.68601446153846</v>
       </c>
       <c r="K521">
         <v>4.003114308300395</v>
@@ -30627,10 +29587,8 @@
           <t>0.69099999999999995</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr">
-        <is>
-          <t>10.917127384615384</t>
-        </is>
+      <c r="J522">
+        <v>10.91712738461538</v>
       </c>
       <c r="K522">
         <v>4.107746917510855</v>
@@ -30685,10 +29643,8 @@
           <t>0.89100000000000001</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr">
-        <is>
-          <t>16.49053661538462</t>
-        </is>
+      <c r="J523">
+        <v>16.49053661538462</v>
       </c>
       <c r="K523">
         <v>4.812053333333335</v>
@@ -30743,10 +29699,8 @@
           <t>0.82</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr">
-        <is>
-          <t>12.701816307692308</t>
-        </is>
+      <c r="J524">
+        <v>12.70181630769231</v>
       </c>
       <c r="K524">
         <v>4.027405170731708</v>
@@ -30801,10 +29755,8 @@
           <t>0.81599999999999995</t>
         </is>
       </c>
-      <c r="J525" t="inlineStr">
-        <is>
-          <t>11.208965999999998</t>
-        </is>
+      <c r="J525">
+        <v>11.208966</v>
       </c>
       <c r="K525">
         <v>3.571484264705882</v>
@@ -30859,10 +29811,8 @@
           <t>0.86399999999999999</t>
         </is>
       </c>
-      <c r="J526" t="inlineStr">
-        <is>
-          <t>11.568356769230769</t>
-        </is>
+      <c r="J526">
+        <v>11.56835676923077</v>
       </c>
       <c r="K526">
         <v>3.481218472222222</v>
@@ -30917,10 +29867,8 @@
           <t>0.84399999999999997</t>
         </is>
       </c>
-      <c r="J527" t="inlineStr">
-        <is>
-          <t>7.8639696923076929</t>
-        </is>
+      <c r="J527">
+        <v>7.863969692307693</v>
       </c>
       <c r="K527">
         <v>2.422549905213271</v>
@@ -30975,10 +29923,8 @@
           <t>0.55900000000000005</t>
         </is>
       </c>
-      <c r="J528" t="inlineStr">
-        <is>
-          <t>12.011985692307691</t>
-        </is>
+      <c r="J528">
+        <v>12.01198569230769</v>
       </c>
       <c r="K528">
         <v>5.586970089445437</v>
@@ -31033,10 +29979,8 @@
           <t>0.74099999999999999</t>
         </is>
       </c>
-      <c r="J529" t="inlineStr">
-        <is>
-          <t>11.893234615384614</t>
-        </is>
+      <c r="J529">
+        <v>11.89323461538461</v>
       </c>
       <c r="K529">
         <v>4.173064777327935</v>
@@ -31091,10 +30035,8 @@
           <t>0.66300000000000003</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr">
-        <is>
-          <t>9.7450666153846139</t>
-        </is>
+      <c r="J530">
+        <v>9.745066615384614</v>
       </c>
       <c r="K530">
         <v>3.821594751131221</v>
@@ -31149,10 +30091,8 @@
           <t>0.73099999999999998</t>
         </is>
       </c>
-      <c r="J531" t="inlineStr">
-        <is>
-          <t>11.161094769230768</t>
-        </is>
+      <c r="J531">
+        <v>11.16109476923077</v>
       </c>
       <c r="K531">
         <v>3.969746429548564</v>
@@ -31207,10 +30147,8 @@
           <t>0.60799999999999998</t>
         </is>
       </c>
-      <c r="J532" t="inlineStr">
-        <is>
-          <t>10.51029323076923</t>
-        </is>
+      <c r="J532">
+        <v>10.51029323076923</v>
       </c>
       <c r="K532">
         <v>4.494533289473685</v>
@@ -31265,10 +30203,8 @@
           <t>0.749</t>
         </is>
       </c>
-      <c r="J533" t="inlineStr">
-        <is>
-          <t>10.545329076923078</t>
-        </is>
+      <c r="J533">
+        <v>10.54532907692308</v>
       </c>
       <c r="K533">
         <v>3.660594873164219</v>
@@ -31323,10 +30259,8 @@
           <t>0.91200000000000003</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr">
-        <is>
-          <t>13.13127876923077</t>
-        </is>
+      <c r="J534">
+        <v>13.13127876923077</v>
       </c>
       <c r="K534">
         <v>3.743566315789474</v>
@@ -31381,10 +30315,8 @@
           <t>0.86899999999999999</t>
         </is>
       </c>
-      <c r="J535" t="inlineStr">
-        <is>
-          <t>8.8502976923076915</t>
-        </is>
+      <c r="J535">
+        <v>8.850297692307691</v>
       </c>
       <c r="K535">
         <v>2.647960184119678</v>
@@ -31439,10 +30371,8 @@
           <t>0.80600000000000005</t>
         </is>
       </c>
-      <c r="J536" t="inlineStr">
-        <is>
-          <t>14.590614461538461</t>
-        </is>
+      <c r="J536">
+        <v>14.59061446153846</v>
       </c>
       <c r="K536">
         <v>4.706649826302729</v>
@@ -31497,10 +30427,8 @@
           <t>0.624</t>
         </is>
       </c>
-      <c r="J537" t="inlineStr">
-        <is>
-          <t>13.598391692307692</t>
-        </is>
+      <c r="J537">
+        <v>13.59839169230769</v>
       </c>
       <c r="K537">
         <v>5.665996538461538</v>
@@ -31555,10 +30483,8 @@
           <t>0.74299999999999999</t>
         </is>
       </c>
-      <c r="J538" t="inlineStr">
-        <is>
-          <t>10.800468</t>
-        </is>
+      <c r="J538">
+        <v>10.800468</v>
       </c>
       <c r="K538">
         <v>3.779436985195155</v>
@@ -31613,10 +30539,8 @@
           <t>0.72199999999999998</t>
         </is>
       </c>
-      <c r="J539" t="inlineStr">
-        <is>
-          <t>8.0039704615384597</t>
-        </is>
+      <c r="J539">
+        <v>8.00397046153846</v>
       </c>
       <c r="K539">
         <v>2.88231623268698</v>
@@ -31671,10 +30595,8 @@
           <t>0.751</t>
         </is>
       </c>
-      <c r="J540" t="inlineStr">
-        <is>
-          <t>9.3071898461538449</t>
-        </is>
+      <c r="J540">
+        <v>9.307189846153845</v>
       </c>
       <c r="K540">
         <v>3.222196218375499</v>
@@ -31729,10 +30651,8 @@
           <t>0.71499999999999997</t>
         </is>
       </c>
-      <c r="J541" t="inlineStr">
-        <is>
-          <t>12.514467230769229</t>
-        </is>
+      <c r="J541">
+        <v>12.51446723076923</v>
       </c>
       <c r="K541">
         <v>4.550715356643356</v>
@@ -31787,10 +30707,8 @@
           <t>0.59799999999999998</t>
         </is>
       </c>
-      <c r="J542" t="inlineStr">
-        <is>
-          <t>9.9626026153846148</t>
-        </is>
+      <c r="J542">
+        <v>9.962602615384615</v>
       </c>
       <c r="K542">
         <v>4.331566354515051</v>
@@ -31845,10 +30763,8 @@
           <t>0.59199999999999997</t>
         </is>
       </c>
-      <c r="J543" t="inlineStr">
-        <is>
-          <t>11.354338615384615</t>
-        </is>
+      <c r="J543">
+        <v>11.35433861538461</v>
       </c>
       <c r="K543">
         <v>4.98670277027027</v>
@@ -31903,10 +30819,8 @@
           <t>0.71499999999999997</t>
         </is>
       </c>
-      <c r="J544" t="inlineStr">
-        <is>
-          <t>12.232611692307691</t>
-        </is>
+      <c r="J544">
+        <v>12.23261169230769</v>
       </c>
       <c r="K544">
         <v>4.448222433566434</v>
@@ -31961,10 +30875,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J545" t="inlineStr">
-        <is>
-          <t>6.5742276785323916</t>
-        </is>
+      <c r="J545">
+        <v>6.574227678532392</v>
       </c>
       <c r="K545">
         <v>47.72402314786476</v>
@@ -32019,10 +30931,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J546" t="inlineStr">
-        <is>
-          <t>8.7601634162316007</t>
-        </is>
+      <c r="J546">
+        <v>8.760163416231601</v>
       </c>
       <c r="K546">
         <v>39.50740979248489</v>
@@ -32077,10 +30987,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J547" t="inlineStr">
-        <is>
-          <t>8.2563538032235471</t>
-        </is>
+      <c r="J547">
+        <v>8.256353803223547</v>
       </c>
       <c r="K547">
         <v>49.36685007418594</v>
@@ -32135,10 +31043,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J548" t="inlineStr">
-        <is>
-          <t>7.5508393697067353</t>
-        </is>
+      <c r="J548">
+        <v>7.550839369706735</v>
       </c>
       <c r="K548">
         <v>41.7361679769464</v>
@@ -32193,10 +31099,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J549" t="inlineStr">
-        <is>
-          <t>7.5989036470494442</t>
-        </is>
+      <c r="J549">
+        <v>7.598903647049444</v>
       </c>
       <c r="K549">
         <v>17.34667033335302</v>
@@ -32251,10 +31155,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J550" t="inlineStr">
-        <is>
-          <t>4.9706359017249708</t>
-        </is>
+      <c r="J550">
+        <v>4.970635901724971</v>
       </c>
       <c r="K550">
         <v>10.72248114393676</v>
@@ -32309,10 +31211,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J551" t="inlineStr">
-        <is>
-          <t>8.4759059407967019</t>
-        </is>
+      <c r="J551">
+        <v>8.475905940796702</v>
       </c>
       <c r="K551">
         <v>32.00920162613013</v>
@@ -32367,10 +31267,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J552" t="inlineStr">
-        <is>
-          <t>6.4417754558780391</t>
-        </is>
+      <c r="J552">
+        <v>6.441775455878039</v>
       </c>
       <c r="K552">
         <v>15.67264137726037</v>
@@ -32425,10 +31323,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J553" t="inlineStr">
-        <is>
-          <t>5.0666815866710939</t>
-        </is>
+      <c r="J553">
+        <v>5.066681586671094</v>
       </c>
       <c r="K553">
         <v>11.631173471393</v>
@@ -32483,10 +31379,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J554" t="inlineStr">
-        <is>
-          <t>7.5786099396148385</t>
-        </is>
+      <c r="J554">
+        <v>7.578609939614839</v>
       </c>
       <c r="K554">
         <v>21.64686021807794</v>
@@ -32541,10 +31435,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J555" t="inlineStr">
-        <is>
-          <t>5.9478991493934323</t>
-        </is>
+      <c r="J555">
+        <v>5.947899149393432</v>
       </c>
       <c r="K555">
         <v>19.74573565855543</v>
@@ -32599,10 +31491,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>6.9798407406118992</t>
-        </is>
+      <c r="J556">
+        <v>6.979840740611899</v>
       </c>
       <c r="K556">
         <v>15.5991879721771</v>
@@ -32657,10 +31547,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>6.8796026294643298</t>
-        </is>
+      <c r="J557">
+        <v>6.87960262946433</v>
       </c>
       <c r="K557">
         <v>15.14718170495404</v>
@@ -32715,10 +31603,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J558" t="inlineStr">
-        <is>
-          <t>4.2079338547045335</t>
-        </is>
+      <c r="J558">
+        <v>4.207933854704534</v>
       </c>
       <c r="K558">
         <v>21.30049161988865</v>
@@ -32773,10 +31659,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J559" t="inlineStr">
-        <is>
-          <t>5.7931640931340187</t>
-        </is>
+      <c r="J559">
+        <v>5.793164093134019</v>
       </c>
       <c r="K559">
         <v>38.62109395422679</v>
@@ -32831,10 +31715,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr">
-        <is>
-          <t>4.1846351557664097</t>
-        </is>
+      <c r="J560">
+        <v>4.18463515576641</v>
       </c>
       <c r="K560">
         <v>31.30490421871054</v>
@@ -32889,10 +31771,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>5.0824486264012156</t>
-        </is>
+      <c r="J561">
+        <v>5.082448626401216</v>
       </c>
       <c r="K561">
         <v>37.17014667069544</v>
@@ -32947,10 +31827,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr">
-        <is>
-          <t>4.3349016791023862</t>
-        </is>
+      <c r="J562">
+        <v>4.334901679102386</v>
       </c>
       <c r="K562">
         <v>31.23679151117895</v>
@@ -33005,10 +31883,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J563" t="inlineStr">
-        <is>
-          <t>5.1899931322442301</t>
-        </is>
+      <c r="J563">
+        <v>5.18999313224423</v>
       </c>
       <c r="K563">
         <v>42.74111991259954</v>
@@ -33063,10 +31939,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr">
-        <is>
-          <t>6.3637131994887444</t>
-        </is>
+      <c r="J564">
+        <v>6.363713199488744</v>
       </c>
       <c r="K564">
         <v>47.60640408777839</v>
@@ -33121,10 +31995,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J565" t="inlineStr">
-        <is>
-          <t>5.795351356245158</t>
-        </is>
+      <c r="J565">
+        <v>5.795351356245158</v>
       </c>
       <c r="K565">
         <v>39.16858158013969</v>
@@ -33179,10 +32051,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J566" t="inlineStr">
-        <is>
-          <t>5.6698099482810944</t>
-        </is>
+      <c r="J566">
+        <v>5.669809948281094</v>
       </c>
       <c r="K566">
         <v>47.90011852858164</v>
@@ -33237,10 +32107,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J567" t="inlineStr">
-        <is>
-          <t>4.7413437251983028</t>
-        </is>
+      <c r="J567">
+        <v>4.741343725198303</v>
       </c>
       <c r="K567">
         <v>34.16556507863481</v>
@@ -33295,10 +32163,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J568" t="inlineStr">
-        <is>
-          <t>4.5243015266095759</t>
-        </is>
+      <c r="J568">
+        <v>4.524301526609576</v>
       </c>
       <c r="K568">
         <v>43.46877937330768</v>
@@ -33353,10 +32219,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J569" t="inlineStr">
-        <is>
-          <t>4.3445690416512104</t>
-        </is>
+      <c r="J569">
+        <v>4.34456904165121</v>
       </c>
       <c r="K569">
         <v>24.61085353074096</v>
@@ -33411,10 +32275,8 @@
           <t>HPLC</t>
         </is>
       </c>
-      <c r="J570" t="inlineStr">
-        <is>
-          <t>4.3445690416512104</t>
-        </is>
+      <c r="J570">
+        <v>4.34456904165121</v>
       </c>
       <c r="K570">
         <v>24.61085353074096</v>
